--- a/data/google_news_dedup_24_0426_UTC_past2d.xlsx
+++ b/data/google_news_dedup_24_0426_UTC_past2d.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K65"/>
+  <dimension ref="A1:K47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -480,32 +480,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Brand Retail Crime</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>("Gucci" OR "Ralph Lauren" OR "Dior" OR "Armani" OR "Louis Vuitton" OR "Burberry" OR "Prada" OR "Nike" OR "Canada Goose" OR "Hugo Boss" OR "Moncler" OR "Saint Laurent" OR "Loro Piana" OR "Lacoste" OR "Versace" OR "Jimmy Choo" OR "Michael Kors" OR "Missoni" OR "Kiton" OR "Aquazzura" OR "Tumi" OR "Rolex" OR "Cartier" OR "Chanel") AND ("theft" OR "stolen" OR "shoplifting" OR "smash and grab" OR "ram raid" OR "robbery" OR "burglary" OR "heist" OR "pickpocket" OR "organised crime" OR "gang" OR "arrest" OR "convicted" OR "sentenced" OR "counterfeit" OR "fake" OR "money laundering") AND -sport AND -"watch review" AND -"price drop"</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery") AND -"postal vote"</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Anne Hathaway’s ‘Devil Wears Prada 2’ Jw Pei Bag - The Daily Beast</t>
+          <t>Former FedEx driver pleads guilty to killing 7-year-old girl after a delivery at her Texas home - MSN</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Anne Hathaway’s ‘Devil Wears Prada 2’ Jw Pei Bag - The Daily Beast</t>
+          <t>Former FedEx driver pleads guilty to killing 7-year-old girl after a delivery at her Texas home - MSN</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Thu, 23 Apr 2026 23:23:00 GMT</t>
+          <t>Fri, 24 Apr 2026 11:53:45 GMT</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxNWlEtUWhWQVVGYm5Pb0txbklnNmhXanY4Y2RVa3NHTGg2Z2NhVGFKVWtsa040cm9pT0U4LUgtOFg2RkduRS1MdWxTWHE5eTNmVm9mbm80U1I2bXBWR1BtR0pzTmVpUEJSblRDaG83bnpnZWNyS2NzbVcyMmxsWmdZMTZxMGpjbUMyZmc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxPRkxiSko2Nnpua29pdFp0aXp4LU9Ld0gwU1JQTHJyWjdhZlpDMUw2d0Rkdk5ZRWJ1dGhqRVpGd2g1WWJqSG1yc2VWa2dOWXpPcDdEQlJ3em5NWW1rZ3ZIZ3F0S3p4SW5Wbmt0d3l3bXdUbjkzVjQ3dTRhdUlZWGNpeEd3eWxsSnNJcWFROEpHUDdUajVaY3FtMTdneVM3UEtYYkRqbTRTek9EX2lCSU1LV0N3Z3J1OV9pdmpBQk8wMm4teHhQbzZrU0ZTdS0zWnRydmp1MVhjQlBQZjc1?oc=5</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -529,38 +529,38 @@
         </is>
       </c>
       <c r="K2" s="1" t="n">
-        <v>46135.97430555556</v>
+        <v>46136.49565972222</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Brand Retail Crime</t>
+          <t>Shoplifting UK</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>("Gucci" OR "Ralph Lauren" OR "Dior" OR "Armani" OR "Louis Vuitton" OR "Burberry" OR "Prada" OR "Nike" OR "Canada Goose" OR "Hugo Boss" OR "Moncler" OR "Saint Laurent" OR "Loro Piana" OR "Lacoste" OR "Versace" OR "Jimmy Choo" OR "Michael Kors" OR "Missoni" OR "Kiton" OR "Aquazzura" OR "Tumi" OR "Rolex" OR "Cartier" OR "Chanel") AND ("theft" OR "stolen" OR "shoplifting" OR "smash and grab" OR "ram raid" OR "robbery" OR "burglary" OR "heist" OR "pickpocket" OR "organised crime" OR "gang" OR "arrest" OR "convicted" OR "sentenced" OR "counterfeit" OR "fake" OR "money laundering") AND -sport AND -"watch review" AND -"price drop"</t>
+          <t>("shoplifting" OR "retail theft" OR "retail crime" OR "shop theft" OR "pickpocket") AND ("UK" OR "England" OR "Britain") AND ("gang" OR "organised" OR "trend" OR "rise" OR "survey" OR "report")</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Best consumer stock to buy right now: Nike or TJX Companies? - MSN</t>
+          <t>M&amp;S chairman blames self-service checkouts for rise in shoplifting - Wandsworth Times</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Best consumer stock to buy right now: Nike or TJX Companies? - MSN</t>
+          <t>M&amp;S chairman blames self-service checkouts for rise in shoplifting - Wandsworth Times</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Thu, 23 Apr 2026 15:27:17 GMT</t>
+          <t>Fri, 24 Apr 2026 08:55:07 GMT</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiANBVV95cUxPNGR3RlNncmhXZGVfcHRhb3hKOTFyVjMxRjNrel9RaVFiX2Fta1l4S3lmcmtiRkJ1dE1LWTZucFB4a1hNOHBLb04xbGxpRFFfT2F5akptTno2c19OY2VoTnpfakExTnhvaWR4MWJPejFGbFZhZGZLdjFCNV9oN0lJZWE5NnhSOWNySER5RndSV2Q1WXJIS0Q3QWRuM2t6b0xDb0pCaHMtTXlqTnVLQ3JyeE5tZjNXX1pXVXAzcFB5cU1mYUE1bWFQZnZiS2xtUmFiMjdmMFdXOUpzUWRIYjIyZGJTQ2o2bDZjeW9uQnZuRkZncDJtdi1JUGJraUxLeDhTcW83QVo5ZlRGT3dFVVFiRjVEV244UmNGZGxqc09vZG01THVxWENucGhoNnVDLU53dmFKMDdSQk50SWJ2bEplWHNoWHlZRU5XVjluVjU0VmhCcWp4UjJ6b2lDNnVsZ2R5dTVnR2RFSzFjSlhKcDIwckpZR054OWIwa2RQeVVuQmUxWnBtR2xIZg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxQdkNWQUtZLTNseGxHbVVXbFE1TU1ZcFlfcllKc2FyVmIwNFQ5bC1zV2Y4MUlLS3BLOFo2U1k1N0hPOTlPQ095TlFRUnoxeWJ3MDdaelVYYTJrYTJYMDFTRHBWNDlBT0RrRVJBejFENkpwUkFSUFlvNGdYWGdQOVZ1a0EybGRMaFBDamJ0c24wX2NjOS1ISWVjV0hLeDlQY2xpeldZRmdBOG9wdnVZNFFTMFc2TFpoRjhKWTZBdA?oc=5</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -584,38 +584,38 @@
         </is>
       </c>
       <c r="K3" s="1" t="n">
-        <v>46135.64394675926</v>
+        <v>46136.3716087963</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BV Value Retail Crime (fallback)</t>
+          <t>High Level City Belgium Dutch</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>("Bicester Village")</t>
+          <t>("Brussel" OR "Antwerpen" OR "Maastricht") AND (bom OR bommelding OR "verdacht pakket" OR "onbeheerd pakket" OR explosie OR schietpartij OR steekpartij OR liquidatie OR arrestatie)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Lululemon shares drop as new CEO appointment leaves investors unimpressed - The Globe and Mail</t>
+          <t>Amerikaanse soldaat opgepakt nadat hij gokte op arrestatie van Maduro en daarmee 400.000 dollar verdiende: militair was zelf betrokken bij operatie - GVA</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Lululemon shares drop as new CEO appointment leaves investors unimpressed - The Globe and Mail</t>
+          <t>American soldier arrested after gambling on Maduro's arrest and earning $400,000: soldier himself was involved in operation - GVA</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Thu, 23 Apr 2026 09:31:16 GMT</t>
+          <t>Fri, 24 Apr 2026 09:03:32 GMT</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxNZXJJNTl3c2FsMHd5SGwtcDZyX3hmdkRtUUg1LXc1UEYyNU8tdWUycnNOSjJJUnhLai1EUzIzdW5sU0JzWUY2am9oeU5DQXppZEhkWEpXYVhQU3V4M2JXQnA5SmhDcEpwOENVb0JvSG9wVll3cWIwUW5RM0wxNHp2ZzhfandnUGYxNHRUTlRZcXNqOHQ3dnU1bDBjOE4zc0tpVWtQVk9KWjVxUGxnck9NYzBR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwJBVV95cUxOMFdPcVpZT1hiMWpVTUc4MUpGYXdfQ0NfQVg0RmlEY09ockh2NDZmckdtdG9vbUVObHF6dXE2dlRxLXduNWdpOFdVNGpnS05PYlhWVUpScnBQSXI1Und1NkVZMTVlRlhQUHZicWY0YVZ2YXZSM1FNZHp0bmpSUjhMQlgyVzZCSWZkRk5LNVMyVFdPZXM0ZWhjZ3FnR3FQY0pTdTZFY2JFZk81aWF5MWJHTjM2YnM1cUV2bEZoUkRzRWlIb3I2Zm5iUkt3bG5HWmtQcTJ5Ul9sVVlCSnhMLU13X2RDVDY2aDVDbVktb3dENmkwQU1rTXQ3ZDFqZFJ2aTk4bjhrYlZFclpZbXIzVEx6dVljWDN6cGtocmNN?oc=5</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -625,52 +625,52 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>en-GB</t>
+          <t>nl</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>GB:en</t>
+          <t>BE:nl</t>
         </is>
       </c>
       <c r="K4" s="1" t="n">
-        <v>46135.39671296296</v>
+        <v>46136.3774537037</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BV Logistics Companies</t>
+          <t>High Level City Belgium Dutch</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery") AND -"postal vote"</t>
+          <t>("Brussel" OR "Antwerpen" OR "Maastricht") AND (bom OR bommelding OR "verdacht pakket" OR "onbeheerd pakket" OR explosie OR schietpartij OR steekpartij OR liquidatie OR arrestatie)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Royal Mail issues delivery delay warning to anyone in 13 postcodes — full list - The Mirror</t>
+          <t>Vier Limburgse Aldi-winkels houden deuren gesloten: “Het is een lopend vuurtje” - HBVL</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Royal Mail issues delivery delay warning to anyone in 13 postcodes — full list - The Mirror</t>
+          <t>Four Limburg Aldi stores are keeping their doors closed: “It's wildfire” - HBVL</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Thu, 23 Apr 2026 10:52:31 GMT</t>
+          <t>Fri, 24 Apr 2026 10:06:17 GMT</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxQWDQ1TUNFOXNNdTRHcEkxTXRUOTR3NjNHeEZWUHUxck9OaXNaTkFTYlN0RTE5UktPV3pJbjdWZmlmYVBuNzRmcFRKXzRxV1BveDV5Z01UUDRyZ0U1aHd5MUdrVXR6V0ZOcWZ5UGwyVUt4anhZQXp0dTd6Sk5tZWxuXzNCUUQwZ9IBiwFBVV95cUxPLTNqQm5DdDlLOEpyb1VxeXdwZzMxWEt6SmtHUHFlLWdnbWc5LS1Pd0VBVGdlaG5McTJBTW5sbG00aklxV3ZxS2RhTG5oSVRnMGZoUmwwTUtKN0JWM1g5dzdhR25oTFMya3ZNUWVBNXM1bld6S0c5LTJOaENqNHlwTURVUnlxbkNtLWJr?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxQUGV6TXFEVHpRZ3M1cERCR3E3NnQ2cHg5Q2FEQjNHWG8wOFc1Rm5mZ28tU0hNSGxBcHR4NzdoOFRDRnp4dGY0ZkJLamRURXdJOWVSOWV3NkZkWWxYTDJGM1M3QV8ybW5PWms2SW9kZ3d3WVBfSlJVeTFtZXlua0VtSE04NHhsblNKOEl4SlA3enZjMmZmNlZXc0RZYjdZQnFzMUdFNF9xaGlaM3hsV2h3dktKbzhUcWZteGpiMQ?oc=5</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -680,52 +680,52 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>en-GB</t>
+          <t>nl</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>GB:en</t>
+          <t>BE:nl</t>
         </is>
       </c>
       <c r="K5" s="1" t="n">
-        <v>46135.45313657408</v>
+        <v>46136.42103009259</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BV Logistics Companies</t>
+          <t>High Level City Belgium Dutch</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery") AND -"postal vote"</t>
+          <t>("Brussel" OR "Antwerpen" OR "Maastricht") AND (bom OR bommelding OR "verdacht pakket" OR "onbeheerd pakket" OR explosie OR schietpartij OR steekpartij OR liquidatie OR arrestatie)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amazon introduces 1-hour and 3-hour delivery in US - MSN</t>
+          <t>Tweede man aangehouden voor dodelijke steekpartij in Hoensbroek, Delano R. (64) nog altijd in voorarrest - De Limburger</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Amazon introduces 1-hour and 3-hour delivery in US - MSN</t>
+          <t>Second man arrested for fatal stabbing in Hoensbroek, Delano R. (64) still in custody - De Limburger</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Fri, 24 Apr 2026 00:09:18 GMT</t>
+          <t>Fri, 24 Apr 2026 11:50:18 GMT</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi_wJBVV95cUxNenNNcm5IbnJ2WTJuVW9vSFh4eG9MV3R2dlRkeUlDOVc0U2FZVVVESm9MTWxXOTdvcF9MaU9WWUQweGdkQlpSR21iSmVFb3IzYzhwZVQ4QXM4dnM3V1FMSWdfQjZQTHN6MzIzVGVQc1NaVFhxeGJDRW0wMkNDYVFYWDJRUk5MTXhUZEp6b1F0ckt5ZlJtUjJBSTVoMkZ5RmJENkk4LWhJQTVxRmF5S1ROQmZIRk14ODhzRklWUkxuOFBMYnJ6Z0doclo3M05kbmd6ek82QkF2TEdvWmJBRzdVNWxzaXFFRV9JSUVESnplYVhKV2ZHeUVkYXRIQXZfMW9lTXNiV0RwOVh5bEtRZGctdzItOTNUYzVGbzM1M1lkeVFId0tSOExlTmdoWjR4X1pRZ2c2VmU4UHFiemtmWFFOdEgzUzcta3pNeWFCbFJOWXZ2M21UcEdpMUxuNWw0a3FCVGNKRzkxNUpWSExYdXdFcC1aOVdvWkpVUU9XT0g5bw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi-gFBVV95cUxOQm93UmhYRl9jNHpxMlVCdXRKOUpZM2Mzb0FwTzF0aDd3RGRpTGU1Y3RYeFlBNTZiNjVvRmNqMW12dm14NU5rbjFsckU5b01vcXlWT05ZU3dnUWNRV2YycXB0bXUxa1phNXJRVmdwOVVCdFlkOHQ4Zk1Ed3A3STliRHJhYlV4akx3aDJWdFBBSmYwOFdCbVN3blJTU3J2dmp5d1QyMmZzV0kxQkVJR0otNEYzNmlIZk1ReVBHajRRX3BiWmotUWlPcC1FNHhFX25ZWFRvMndGOHJ0dDExWGdzemNISjJJTFRyN1VNMVVWcDhFdVVzN2J3TTlB?oc=5</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -735,52 +735,52 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>en-GB</t>
+          <t>nl</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>GB:en</t>
+          <t>BE:nl</t>
         </is>
       </c>
       <c r="K6" s="1" t="n">
-        <v>46136.00645833334</v>
+        <v>46136.49326388889</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BV Logistics Companies</t>
+          <t>High Level City Belgium Dutch</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery") AND -"postal vote"</t>
+          <t>("Brussel" OR "Antwerpen" OR "Maastricht") AND (bom OR bommelding OR "verdacht pakket" OR "onbeheerd pakket" OR explosie OR schietpartij OR steekpartij OR liquidatie OR arrestatie)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Barricaded former UPS worker who allegedly stole delivery truck arrested after Fremont standoff - ABC7 San Francisco</t>
+          <t>Ontmanteling bom op strand van Lombardsijde - HLN</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Barricaded former UPS worker who allegedly stole delivery truck arrested after Fremont standoff - ABC7 San Francisco</t>
+          <t>Dismantling bomb on Lombardsijde beach - HLN</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Thu, 23 Apr 2026 21:00:58 GMT</t>
+          <t>Fri, 24 Apr 2026 12:03:49 GMT</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxNNGpoeldBTE9tNmFIa3E4cFdTbzIxRUNKVGlidkFQRmIxYmo4QUZkbDNIeHIzaVNVWF94ZnI0R0hsZXVjb0I1TTVDLWw5YXpjdEh1NTFaTVh2TnY3TUk2MlUtdEVOaUgxZ0hrX0Fac0FXdFB4UTEzV2hzeW5qemxBeUk1WTlfdjBZZEI5d1J5ek1Md3ZURDBkQUZQY0V4X04yTjZzYWgxX3VONkJQb0ZZZ9IBtgFBVV95cUxOb0JBa1Vpa0pGMmNTUEdybldob1pKSDBtbGI3RUg1SlFWTGdDeUZaS2RLblVEYS1xTzhYWm5MRmg1cWFldnI1THpEOGtXOVdoWmtyaTJ2RFBmSUZOVHVGSHM1WTJySy1EYmM3dU44RjQtZWhQbXZKNXo4a2J6VnZ4eGtJdk1pMjEzZjdhRDUtNm5JWEpmNWVNWFlkM2kxM0lMby02X2hqZ1NBcmtjMDI3Q013bFBVQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxPZzJMSTcwYlZ1RzhFeHdXYmZCdjR0MzNoZGpldVlqaTk3TkZ5QWIxaWFyc1BxU3R5bUpFeHZKdTRJdmptWF9BMTF4NmZzX3pRVXRrNXQzd0ltUm95MExEY1djazRGOENMR1hQeWVjTnVneHp2QkktMVlHUmF0eEdLMzRXbVZ2NWR4X0hlRFVlTGNPZw?oc=5</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -790,52 +790,52 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>en-GB</t>
+          <t>nl</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>GB:en</t>
+          <t>BE:nl</t>
         </is>
       </c>
       <c r="K7" s="1" t="n">
-        <v>46135.87567129629</v>
+        <v>46136.50265046296</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BV Logistics Companies</t>
+          <t>High Level City Belgium Dutch</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery") AND -"postal vote"</t>
+          <t>("Brussel" OR "Antwerpen" OR "Maastricht") AND (bom OR bommelding OR "verdacht pakket" OR "onbeheerd pakket" OR explosie OR schietpartij OR steekpartij OR liquidatie OR arrestatie)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>FedEx joins Amazon, Walmart in race to get goods to Americans faster with new same-day delivery service - MSN</t>
+          <t>Tentenkamp ontstaat in voormalig tankstation: burgemeester wil overgaan tot ontruiming - Nieuwsblad</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>FedEx joins Amazon, Walmart in race to get goods to Americans faster with new same-day delivery service - MSN</t>
+          <t>Tent camp arises in former gas station: mayor wants to evict - Nieuwsblad</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Fri, 24 Apr 2026 01:17:29 GMT</t>
+          <t>Fri, 24 Apr 2026 13:39:45 GMT</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixANBVV95cUxQcjFvMmlJbjg3NE5rWkdPWWRIUkloTVJuRDJYSFQxSHA2UlEyeEQ3WmsxUG8ycWtEcnN5bHVtYkd2YzByQW1NOWphekozNVZKcmhfVWNySWM0QlB4U1BpZHV1bEZZUnNlcU9nSzJ1UktFdnZIS1BvMEw3UWFTZHNMdGNFdmdOOUpSVDNCTlZ3YXN2MUZlNThJX0JHbFQ2YWI4Rm53c2VnOEFmQzZSNm1jWld0VXZXQTU4N2VkTURzMEwtRWJKb3RxaXVmVDNhQWEwRHdFakh1SFJMX0pwYlB2aGtvYTBFalk2RWpfYnRxc0t4WGQ5d3VhNFlOYjFjYzZCMjVYaGVOb05vdHhsaU96a1JUVGRHeUsyZURaVHFMSTBBMUJhTnQyNGthQmFYN1VZUzRBTi1rcDRxTzVINVUxOGFqSnF1SVE0alhwRE9MX3B3SEV4MTNQSkNienhxb1h3RjF2LXF3QkoxS0RneU02dzRZTkMxbUE2WXJzalA4dUg0cERGSVBpcHlIMl9ObUZRbnBkU2MycXpoejQxTWJkaDRVRVkwbzUyejZRY1VTOWQ5cEtaNllwempfOTlpUVRua2RzMw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxQejR5c1ZWM09LV1RQUkhwN2Vlbm1aUTNPcUZ5QkNUelVLLVhSZk9MRVRmcmVsVl9TRlN3ek12TnpLakUzTG4xOTZta1NRYU9RaGpNYzV3VS11LXAwNGJkaGVzSUVmTEFQZmVZZXkwX1VVUU5NWV95cWFLRjViVm10NEszekRkX2xmZXluOC1EOWVfckp0ZzZRbUxxVW1sblg2X2RlaG04SHpQQ09URWk5YkIyZWRaSzFaNEctemk1NEZmVG53azV4QzY3a1UybWFfalZRUFlUbUhScF9nSWloMHdR?oc=5</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -845,52 +845,52 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>en-GB</t>
+          <t>nl</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>GB:en</t>
+          <t>BE:nl</t>
         </is>
       </c>
       <c r="K8" s="1" t="n">
-        <v>46136.05380787037</v>
+        <v>46136.56927083333</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BV Logistics Companies</t>
+          <t>High Level City Belgium Dutch</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery") AND -"postal vote"</t>
+          <t>("Brussel" OR "Antwerpen" OR "Maastricht") AND (bom OR bommelding OR "verdacht pakket" OR "onbeheerd pakket" OR explosie OR schietpartij OR steekpartij OR liquidatie OR arrestatie)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>FedEx announces same-day delivery option days after Amazon launches 1-hour and 3-hour delivery - MSN</t>
+          <t>Celstraffen voor bende die cocaïne verhandelde via Snapchat en op Arenaplein: “Geen school, geen werk, geen legale inkomsten” - HLN</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>FedEx announces same-day delivery option days after Amazon launches 1-hour and 3-hour delivery - MSN</t>
+          <t>Prison sentences for gang that traded cocaine via Snapchat and on Arenaplein: “No school, no work, no legal income” - HLN</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Fri, 24 Apr 2026 00:46:29 GMT</t>
+          <t>Fri, 24 Apr 2026 07:27:51 GMT</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugNBVV95cUxPUzZhTDJjYlRRekJEQjF4MWg1Z3lkSUVWVFp2dW5ncEkxdzdNaTJyV3pxdDVOc1hNUlk2eUgwN21ScEdhM1h0NGNvaV9YMjNYaE5DckxpLWhLb0xZVTd6MGhsd3F6YTU3cWtGODBsOG1iMGtDOHVfQ3FxeVFYZGxMQTdzYkctZW1FcllUU0FZUlNqT2thd0NSVU5BOXRVQk9sTlM3ZlpIVzNTUFZjaDhJX3E2X05Lbm0tNFZOS0RhRFN3THEwWmV1RG9nMEcwcEJyRmlGUllFcC1xeDlxSHFJbTZabVU1LVZnZmFEUGJpYnhaZ0JMTkY0S1hjMDVSV0NSdTdXVzVreE1DbGh6VXY5OTRxM0Y3X3JRUjM2bGg3NERCOUJCR2RhVGp0dnFEMVRQVFotN2dQRDFSNlZkeFdoOWdCQnJhREdwUmdyTHVGM3RmVUNkVXY3d3lXb2NneHROMHJKSXJSODdHZkhUTWtJU3BOaGdEaHJlMlNiNkZzVDVsalFRMVB1RVY1SDVzeTVMeDFwXzV3SDVuV24tbzVXcFFJVGlUX1BodjNhcm5pMmxzdk0wZG9GOHhB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi8AFBVV95cUxNQURLWGFERWFleVBhMlRQcDVhSUZPaHVZaTZsLXpRVklVRExjcmFsbkN0TXBfcjlENFlfc1U0VzdUanlEdzBleVNIeE1zVEdxVXFkZ0hxZ3VaODBhck5yZXZMdVZCN0JnWFlzbVhDYmtiTW04Z1J2bUZzU19nVWdUZUIyOEROcGxBUDBGNHNBaG1IMFlWWEpOMWJNUllIeVRYbGVONkE1d1JnTG9NUFhmVngxWWRlamswRTBpMnZWVHZHSDJaZi1DWHk0SlY5bVRfWV8wTzUydTJUempNMHBhdFZqVGx2RVluT3llZlZuOTk?oc=5</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -900,52 +900,52 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>en-GB</t>
+          <t>nl</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>GB:en</t>
+          <t>BE:nl</t>
         </is>
       </c>
       <c r="K9" s="1" t="n">
-        <v>46136.03228009259</v>
+        <v>46136.31100694444</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BV Logistics Companies</t>
+          <t>High Level City Belgium English</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery") AND -"postal vote"</t>
+          <t>("Brussels" OR "Antwerp" OR "Maastricht") AND (bomb OR explosion OR shooting OR stabbing OR "suspicious package" OR "bomb threat" OR "terror") AND -football AND -soccer AND -transfer</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amazon rides on new logistics and delivery innovations: What's ahead? - MSN</t>
+          <t>Investments in nuclear weapons production surge: study - Brussels Signal</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Amazon rides on new logistics and delivery innovations: What's ahead? - MSN</t>
+          <t>Investments in nuclear weapons production surge: study - Brussels Signal</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Thu, 23 Apr 2026 18:00:22 GMT</t>
+          <t>Fri, 24 Apr 2026 07:59:02 GMT</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi7wJBVV95cUxQWmxVczBjLWFLaHR1Qm1iU2hTbElLZ2tHWi1Kd2pXYjAtR1ZmSmlNNUFNUDVQQnpqUFBjRDFqSThRUHdHTDhVSTRWM2JDelBHR0xzZTlIWm1rTUlvNEFmQmptQmRKaExRaURxd2FCYnFHdC1uR25KX1JIZl81cnRzYkJKaF8xaEtYcXZnb1JIZnZaRDdLdWIyYjZNLUVlY3Zqemg1MWdfaVRlVERDTklXTWdLTWI4c0N5clY2MDZMN0ZqaUU3QTEwMmhISExmTEp2NUtDWnk1YnN0Tk5Xb09MUXZuYnJXa01uUTdOX1ZkNVFTdVFhNEZaS0M2UFJIM0hkTWNYWjh2UzNVaWtNcWp2X2RqeGFhbDA5M05LRkF6TEIyUGhpR01sTTY5WkNqX2tQT1FjbC1UWG9qXzRLYjdTbEpzTGF4aU5CYk1fOWRFaDZLMmwyaGZYUXEtRXRjSjg4ZXJxdmRxUnNPcl9KbHNr?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxQOTNWeUVjeVF3WWd5MDlWVXdGaTBvWGZ0ZTlVTVZRekJUSi0wU3A5MFZCYWZOWE95bTZzcE9jcUJHejB5OVpLdFFmVkN1VENickJGMEp5a3BjMXpHWnJDVG03TUtOS1FLTmtHNllZekl3YUlSbVd0bFA3c2Q5NWpEamQ0dnpxbDk3bm1WWlliemFvZw?oc=5</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -960,47 +960,47 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>GB:en</t>
+          <t>BE:en</t>
         </is>
       </c>
       <c r="K10" s="1" t="n">
-        <v>46135.75025462963</v>
+        <v>46136.33266203704</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BV Logistics Companies</t>
+          <t>High Level City Belgium English</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery") AND -"postal vote"</t>
+          <t>("Brussels" OR "Antwerp" OR "Maastricht") AND (bomb OR explosion OR shooting OR stabbing OR "suspicious package" OR "bomb threat" OR "terror") AND -football AND -soccer AND -transfer</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amazon customers furious as delivery drones drop boxes from 10 feet in the air — damaging orders: ‘F–k outta here’ - AOL.com</t>
+          <t>Youth Violence on the Rise in Belgium - The European Conservative</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Amazon customers furious as delivery drones drop boxes from 10 feet in the air — damaging orders: ‘F–k outta here’ - AOL.com</t>
+          <t>Youth Violence on the Rise in Belgium - The European Conservative</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Thu, 23 Apr 2026 14:29:36 GMT</t>
+          <t>Fri, 24 Apr 2026 09:26:39 GMT</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxObzVDZlFJY2NxTS1jRWEyaVFjRWJBMV9MdFB0V3R3TTVNWmVRNS1QNUZPeXpnMlBzYlRvNl83eThCR2ZNNjRubVhhSHdHZWhsVFczX3diemVGQjZXUGk1VUtCVGdkODVwZXRIc2RJaFh5b3UyS2NEZXlfeXdMbkt4NEtvbDlhY28?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxObC14RzR6elctMk9KSGwzRzRBX1JDMVc3ejBibG8wakdnRlRIdkEyY0RxM2tkd2lOWGJwYncxTExRdDNyZEpGdmdBakloLVBHUFMyaHJNSGJUdEU1N2x1bW9fX3plbnlpSTZhR0ZEVTVQOEl6eG5rSjJpOWk2SGhxNEhlYjMyb3dzYWNFTGhiMlUyNm9iT0YxalBHWUd2QjlfSkl3MWYyVVBXb09OOXZkUmhsb085MDc0LVdz?oc=5</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1015,47 +1015,47 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>GB:en</t>
+          <t>BE:en</t>
         </is>
       </c>
       <c r="K11" s="1" t="n">
-        <v>46135.60388888889</v>
+        <v>46136.39350694444</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BV Logistics Companies</t>
+          <t>High Level City Belgium French</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery") AND -"postal vote"</t>
+          <t>("Bruxelles" OR "Anvers" OR "Maastricht") AND (bombe OR explosion OR fusillade OR agression OR couteau OR "colis suspect" OR "alerte à la bombe" OR attentat) AND -football AND -transfert</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>See photos inside Amazon's newest same-day facility in Reno - Reno Gazette Journal</t>
+          <t>Charleroi: Découvrez la liste des radars prévus la semaine du 27 avril - Télésambre</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>See photos inside Amazon's newest same-day facility in Reno - Reno Gazette Journal</t>
+          <t>Charleroi: Discover the list of radars planned for the week of April 27 - Télésambre</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Thu, 23 Apr 2026 19:34:00 GMT</t>
+          <t>Fri, 24 Apr 2026 10:59:00 GMT</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi5gFBVV95cUxPWlo5cE43TXp4bTFDZWQzXzh4TlhNb3B2OWl5WU1NUG83SmYwLXlGYlB0ckVsd01RWXoyZXVHdUY2MUQ0cjlNcVZnQUQ2M0t5SURvOTZjSWRXVTB2QlZHQThnaUtteGhQaG03YUNDVWFLaVNRSWt4dDUtRm54LXNHWUJFUFpCaVlpNkhMSktJZjdlSnI0WjhibXZvU0xQNzRxY3lhZng0c2xlTDZaN1RrdnVqWmtUeEJHaUp2MkZIaGpBWV9QNjRPN0dLZkI2Q2tPb1Z3ejhKdEliQVRwelNoVmtrd0FfZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxQU0c4Ymk4Z0F5d084SVBCTXc2Rzd3cU4xZF9jb00yNWRTVHo3SVc4YWx3TmpCRVlZU2JuS3pmQ0l6dWpfdFZnaHVlVk9GWnk1blNET0wtZzI1NEpqT2N4dTZmZnpNYUotcFVHTVhrdEIzX0RKWXViNE5VYWJPY1JxNHJRY2dJSld4am1pNGd1eHVLM25oUV90V0Jya240TmN3WjJPQWN5VlU?oc=5</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1065,52 +1065,52 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>en-GB</t>
+          <t>fr</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>GB:en</t>
+          <t>BE:fr</t>
         </is>
       </c>
       <c r="K12" s="1" t="n">
-        <v>46135.81527777778</v>
+        <v>46136.45763888889</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BV Logistics Companies</t>
+          <t>Local Town Maasmechelen Dutch (fallback)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery") AND -"postal vote"</t>
+          <t>("Maasmechelen" OR "Hasselt" OR "Lanaken")</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amazon: The North Platte delivery station has processed more than 175,000 packages since November - MSN</t>
+          <t>Op zucht van promotie naar 1B, maar Sporting Hasselt krijgt geen proflicentie: "We zijn positief voor beroepsprocedure" - sporza.be</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Amazon: The North Platte delivery station has processed more than 175,000 packages since November - MSN</t>
+          <t>On the hunt for promotion to 1B, but Sporting Hasselt does not receive a professional license: "We are positive for the appeal procedure" - sporza.be</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Thu, 23 Apr 2026 13:08:07 GMT</t>
+          <t>Fri, 24 Apr 2026 10:58:00 GMT</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi5AFBVV95cUxQYzVsYmZxT1NVal9WZWVtTmpyUWdKYnNUdThMVk5qQVZMZThLLVVvN3JlMmd0U3duVjNIVkxoQjdKWWVTZDM1X19aVHVOQ25XcUZ2NmZPVzhMcnRjSXNaVUx4Tm5abm41LUNxYXdKOThXcVMyVTNNNTRQbTNiZzVnS1hwcGg0S05DaVlaY0dzMjRGcEdFOXFtdFNfRk9MeElJY1lGa3hiLVhXTHVfUDN4V3FxTHZTWl9ndmw0QWkxeGhNaTUxeVVFRXRxbFdXWUhQY1hRMXNMRThUbUV1djhNVEk3b0M?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi9AFBVV95cUxOcWtrdEJWam1xenZaODJUYkluRjVNUG9mTmMyVXJxLU1MYTZXUHlvQWEtMDFrdDdkY2F1MHVMYVd0OHp1R0lQUmRmczllYUxOSHB3RGlDT3JWdk1KNmFZU2pSaDQxbURmSVVHZEVlaXQ5bThfbXdhWXN0ZnRpaVprbk9meldybURnVmJRU1ROVW85RmxTWTBraXJZalhjVENGTTNjWXlzNzFGd0pEbnF6MVJTRW9SUVQwOF9ENzQxUlkwSHdYcWpqNFFzZDQ4eTVsMkpZdHhzT25seVRVbHlMSlQtVndnNkZaa1A0c3dNRGFyMS1k?oc=5</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1120,52 +1120,52 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>en-GB</t>
+          <t>nl</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>GB:en</t>
+          <t>BE:nl</t>
         </is>
       </c>
       <c r="K13" s="1" t="n">
-        <v>46135.54730324074</v>
+        <v>46136.45694444444</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Shoplifting UK</t>
+          <t>Local Town Maasmechelen Dutch (fallback)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>("shoplifting" OR "retail theft" OR "retail crime" OR "shop theft" OR "pickpocket") AND ("UK" OR "England" OR "Britain") AND ("gang" OR "organised" OR "trend" OR "rise" OR "survey" OR "report")</t>
+          <t>("Maasmechelen" OR "Hasselt" OR "Lanaken")</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Marks and Spencer boss blames self-checkouts for rise in shoplifting among 'good, honest people' - GB News</t>
+          <t>Sporting Hasselt krijgt geen licentie voor 1B - Nieuwsblad</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Marks and Spencer boss blames self-checkouts for rise in shoplifting among 'good, honest people' - GB News</t>
+          <t>Sporting Hasselt does not receive a license for 1B - Nieuwsblad</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Fri, 24 Apr 2026 03:46:01 GMT</t>
+          <t>Fri, 24 Apr 2026 10:35:25 GMT</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE5wYkhySEJ5bUhLcngxaExLVnpNUm52UUxyWjZHd0ozbG5zSjlDUXFaRGNsWlJITndDd3J5ekhzMFBwSUlkWE0ycU82VXZEX1p1SjRDNDVMdi1BdXgtb3B3MzFPbTZuODRaenJGQVp2WlRSQjlyNTBR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxNVlRtd1Q4WUZCdTN1ZVVLLUVEbnVVSW9rRmU4TjQ4ZjR1dHRFY0wyUWFuOW9nOVExem5JODBWS0c0NXRJRjB3VmEwejRFMWU2cFdpR0tnUTNBaC1vdklEWmctNnY3Qjh1WlBCclNtSUY0MzROTE9zc01PV0o0eERKUmttbk9kTWRMdmVpbllORVBGM2NQX3dTSTRyUURZV1d6bmF6SG1R?oc=5</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1175,52 +1175,52 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>en-GB</t>
+          <t>nl</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>GB:en</t>
+          <t>BE:nl</t>
         </is>
       </c>
       <c r="K14" s="1" t="n">
-        <v>46136.15695601852</v>
+        <v>46136.44126157407</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>High Level City Belgium Dutch</t>
+          <t>Local Town Maasmechelen Dutch (fallback)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>("Brussel" OR "Antwerpen" OR "Maastricht") AND (bom OR bommelding OR "verdacht pakket" OR "onbeheerd pakket" OR explosie OR schietpartij OR steekpartij OR liquidatie OR arrestatie)</t>
+          <t>("Maasmechelen" OR "Hasselt" OR "Lanaken")</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amerikaanse soldaat opgepakt nadat hij gokte op arrestatie van Maduro en daarmee 400.000 dollar verdiende: militair was zelf betrokken bij operatie - GVA</t>
+          <t>26-jarige student schuldig aan verkrachting studente, maar hij krijgt geen straf - VRT</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>American soldier arrested after gambling on Maduro's arrest and earning $400,000: soldier himself was involved in operation - GVA</t>
+          <t>26-year-old student guilty of raping student, but he receives no punishment - VRT</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Fri, 24 Apr 2026 02:19:55 GMT</t>
+          <t>Fri, 24 Apr 2026 09:34:08 GMT</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwJBVV95cUxOMFdPcVpZT1hiMWpVTUc4MUpGYXdfQ0NfQVg0RmlEY09ockh2NDZmckdtdG9vbUVObHF6dXE2dlRxLXduNWdpOFdVNGpnS05PYlhWVUpScnBQSXI1Und1NkVZMTVlRlhQUHZicWY0YVZ2YXZSM1FNZHp0bmpSUjhMQlgyVzZCSWZkRk5LNVMyVFdPZXM0ZWhjZ3FnR3FQY0pTdTZFY2JFZk81aWF5MWJHTjM2YnM1cUV2bEZoUkRzRWlIb3I2Zm5iUkt3bG5HWmtQcTJ5Ul9sVVlCSnhMLU13X2RDVDY2aDVDbVktb3dENmkwQU1rTXQ3ZDFqZFJ2aTk4bjhrYlZFclpZbXIzVEx6dVljWDN6cGtocmNN?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxNTVY0U1Z0U25yQlhnMG45aGVqUjhLMUpIQk9fWVhOV2s5YTRxVkpBOE5EMnhTd1JoN25NcTVraDl1MEt5T2l3Rmp4elFZRG93VWxGak1yckFpYU4tRGpGU0dZcFpBNzJ6TkwtOTFhd3U4ZktHUDdFUno1VDhtU1FCYlZnbmgwQQ?oc=5</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1244,38 +1244,38 @@
         </is>
       </c>
       <c r="K15" s="1" t="n">
-        <v>46136.09716435185</v>
+        <v>46136.3987037037</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>High Level City Belgium Dutch</t>
+          <t>Local Town Maasmechelen Dutch (fallback)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>("Brussel" OR "Antwerpen" OR "Maastricht") AND (bom OR bommelding OR "verdacht pakket" OR "onbeheerd pakket" OR explosie OR schietpartij OR steekpartij OR liquidatie OR arrestatie)</t>
+          <t>("Maasmechelen" OR "Hasselt" OR "Lanaken")</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Man die drie jaar lang uit geparkeerde wagens stal, opgepakt: politie vindt grote buit in zijn woning - Nieuwsblad</t>
+          <t>‘Hasselt kan kampioen worden, maar krijgt nog geen licentie voor profvoetbal’ - VoetbalPrimeur.be</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Man who stole from parked cars for three years arrested: police find large loot in his home - Nieuwsblad</t>
+          <t>'Hasselt can become champion, but will not yet receive a license for professional football' - VoetbalPrimeur.be</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Thu, 23 Apr 2026 23:25:00 GMT</t>
+          <t>Fri, 24 Apr 2026 11:37:00 GMT</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi5gFBVV95cUxNU2IwbW1qMkVJd25RVEdCcGs5UDM2TVFzc1BDN3lqOWZNQlFMd3JHWWZkT3dSVGp5S2RUb2RnUG91SkNWbEJfS3VUTU1vcmNQcjJqajFmaXhkeHE4WV81VXh2NTFvS0RGempkdl9rb2tpQ0FFM1V3S1F3TnFQbml2ZFdsMFk2TjBmel9aUVRRa2xBVklPdG9uQlNhUzhOaDBWQ1FGd0w2MUNfRmczMFVOeXhQNjIzNXhSbmZHM1BiSXBHbzBQUVVoYzRfekdyU2dEUmhnUzBVYmZTaHN6bzdqNkc0SHJOZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxNbmhFN0xRc2E0dGRZbGcyalBuSENOUk9iM2kyMGlINWE0RTN1eE9HajZEVG1uUm1Vc0dIOE9tLXFMRm1CcmJPWVNielNubi1BNDZuTHpVeG8wRkd6Y2NZdUNNMnB2N0lvLV8wSXp3aEYzUnBPWmF2XzQyVWg5c1MtTWItTmpvSkdGR3VUZ3EwS0NtcWpRdXRrSnQyekVhUTM3VzUyODA5SXVUYWNwelBVUWUzYUFiWkh5R1RoQllub0J5dw?oc=5</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1299,38 +1299,38 @@
         </is>
       </c>
       <c r="K16" s="1" t="n">
-        <v>46135.97569444445</v>
+        <v>46136.48402777778</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>High Level City Belgium Dutch</t>
+          <t>Local Town Maasmechelen Dutch (fallback)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>("Brussel" OR "Antwerpen" OR "Maastricht") AND (bom OR bommelding OR "verdacht pakket" OR "onbeheerd pakket" OR explosie OR schietpartij OR steekpartij OR liquidatie OR arrestatie)</t>
+          <t>("Maasmechelen" OR "Hasselt" OR "Lanaken")</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Staking bij Bpost duurt voort, nieuw overleg gepland - Nieuwsblad</t>
+          <t>Challenger Pro League - RWDM moet verder zakken na gemiste licentie, Sporting Hasselt grijpt naast proflicentie - Starsporttv</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Strike at Bpost continues, new consultation planned - Nieuwsblad</t>
+          <t>Challenger Pro League - RWDM has to drop further after a missed license, Sporting Hasselt misses out on a professional license - Starsporttv</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Thu, 23 Apr 2026 16:03:43 GMT</t>
+          <t>Fri, 24 Apr 2026 12:56:19 GMT</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxNLU1OdlNwdmtvQXVDSC05aExsRHNBWnhZVy1qYnMybUNjSVMxQkFHWVVmdENRT3hDRWxHVkFMN2M5ZklScUJ0djY4QnVrOWlPdF9EMG5KajNWU0dSZDh5Y3VUZFVGSFhhaE9LbHo0LWpIaHpyeWZsdmh6Z0pCcG9fTUxxR2FJd2JkTGNCVkM0Z1lNY1oxV2djNzNsZFlZZEMxUUg5UkdSZkpNTXkyMHU0Tg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxNQWZ4aU1ldzd1MG9xQ1N5OFBlRWs0bHFZWTlaSmVWWUFsTEFOTTNRNHNaVWcyU0RQdTBCbDhhNHd6Zzhtb1h6Y09WSkx5ME5ZWkNuODVnSEVQRlVNTzNUamxud0syd1EyYXdLUUVtTzdjOGRWcjd5UDFtVl9faDlha1JPcVlWQVdaZjJ6V0NzQk1LVEdwRVdwaDdEY1ZGblBTdzZ3d3NFZFJvQUhQN1JDUHJ5UjJSSmZSOG52MlZtbThweHNRNVJkQmx1cm1heVoxWkMzbXJn?oc=5</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1354,38 +1354,38 @@
         </is>
       </c>
       <c r="K17" s="1" t="n">
-        <v>46135.66924768518</v>
+        <v>46136.5391087963</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>High Level City Belgium Dutch</t>
+          <t>Local Town Maasmechelen Dutch (fallback)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>("Brussel" OR "Antwerpen" OR "Maastricht") AND (bom OR bommelding OR "verdacht pakket" OR "onbeheerd pakket" OR explosie OR schietpartij OR steekpartij OR liquidatie OR arrestatie)</t>
+          <t>("Maasmechelen" OR "Hasselt" OR "Lanaken")</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Slachtoffer dodelijke steekpartij in Hoensbroek is 29-jarige man - De Limburger</t>
+          <t>Extra mobiliteitsmaatregelen voor topper van Sporting Hasselt: “Kom met de fiets, dat is het snelst” - HLN</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Victim of fatal stabbing in Hoensbroek is 29-year-old man - De Limburger</t>
+          <t>Additional mobility measures for Sporting Hasselt's top team: “Come by bike, that's the fastest” - HLN</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Thu, 23 Apr 2026 13:53:44 GMT</t>
+          <t>Fri, 24 Apr 2026 10:03:35 GMT</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxOcldLbG1yX3lhOWdycjg3LS1lUjRaM09qQU5lajFraXlJcVlXNHFBNFhmWXBSZl9SdUJLZmxBSVNzdGVrVHhqcjZ5X09oVUlEU2gweXhDOW9IWXFSRGFDOG1zVzk4SEtfSGFNWFV0TzJ6Vi1iRk82RXY4S1ZWdGZCNXJuaVBJYjYtN3ZFdTNQcnd6bEthcjFWUjZxZi1zUG5iZlhDV3h6Ym9nT2hDTlktekRfcjN3OFBVdndLcUkzYUhJS2Q4cGhMbQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxPaW05MS1Ud2MzbHBwMWZLdEEtbG1HUVlhZ1daSUVOMVV2RjBsazdHemYtODFtZHlRVGdnTkxkS0JjTkYza05rZ2RScl9rZVdiLXotcjJISklodnZoRUFmamwtaHMwTWxPLWVxLWlLZ3RaN3RKbGFYekFvSlMtUlo3WEZQZFl4N3lCbjR2QTg5emFyNVVpLW1lb0cxaG1zZ0JJZ0puaGd0RVhYWkdHLXhWNHNVMkQyOUhiWGppclJuOTVNN1ptSzFYR2ZNV3FnUQ?oc=5</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1409,38 +1409,38 @@
         </is>
       </c>
       <c r="K18" s="1" t="n">
-        <v>46135.57898148148</v>
+        <v>46136.41915509259</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>High Level City Belgium Dutch</t>
+          <t>Local Town Maasmechelen Dutch (fallback)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>("Brussel" OR "Antwerpen" OR "Maastricht") AND (bom OR bommelding OR "verdacht pakket" OR "onbeheerd pakket" OR explosie OR schietpartij OR steekpartij OR liquidatie OR arrestatie)</t>
+          <t>("Maasmechelen" OR "Hasselt" OR "Lanaken")</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Brusselse politie vindt berg gestolen spullen bij vermoedelijke dief - BRUZZ</t>
+          <t>Patro Eisden geeft in diepe slot bonus prijs tegen Beerschot - TV Limburg</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Brussels police find mountain of stolen items with suspected thief - BRUZZ</t>
+          <t>Patro Eisden gives away a bonus in the deep slot against Beerschot - TV Limburg</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Thu, 23 Apr 2026 14:03:50 GMT</t>
+          <t>Fri, 24 Apr 2026 11:08:42 GMT</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxONWRRRjdaWjc5N254eXBHME1CelVsWXhobW9uWDVVb3dIQkNwbFhZOU5GSXpSYUYwa3U4Wi10LXRzcTVSMnV2NUp2QXR3VHBTMm54TTZSX0RQZktkUUk3eEZKOGdyS0NjLVdPNEFTWGNSTEd5RERsNVZpNjk1WUpfVUQ0cWg3clBFWkNJSUZOZGVHaDNEdTZMSGtCNjlhMjlMbFM4NHlsdUg4Y240Uk5SMmpZd2tiemlI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxOUFBTblJDMHlLbWxpdFpYazJGcVhMeWphZUVSZGFtc210MDVtUER1MEpPYm96WEFLazNxMEZYRHo5dklVRXpYLXNRUUpIYVJIdTB2ZGpMWDVlUVA3LW9yUU9YbkdkMl8wOU9aSWFsM25KRW1yZldJZndXVEtpNkhqRThjSEtTMnZuM0FtX28wVGVqNU44WHdWYw?oc=5</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1464,38 +1464,38 @@
         </is>
       </c>
       <c r="K19" s="1" t="n">
-        <v>46135.58599537037</v>
+        <v>46136.464375</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>High Level City Belgium Dutch</t>
+          <t>Local Town Maasmechelen Dutch (fallback)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>("Brussel" OR "Antwerpen" OR "Maastricht") AND (bom OR bommelding OR "verdacht pakket" OR "onbeheerd pakket" OR explosie OR schietpartij OR steekpartij OR liquidatie OR arrestatie)</t>
+          <t>("Maasmechelen" OR "Hasselt" OR "Lanaken")</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Amper week nadat vader acht kinderen doodschoot, vallen één dode en vijf gewonden bij schietpartij in winkelcentrum in Louisiana - GVA</t>
+          <t>Aldi-filiaal in Lanaken blijft dicht door protest tegen zondagsopening - HLN</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Barely a week after father shot eight children dead, one dead and five injured in shooting in Louisiana shopping center - GVA</t>
+          <t>Aldi branch in Lanaken remains closed due to protest against Sunday opening - HLN</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Fri, 24 Apr 2026 04:22:37 GMT</t>
+          <t>Fri, 24 Apr 2026 10:58:02 GMT</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiggJBVV95cUxNZUFrVmNYRVNwYkJmaWtXZVVzQmZEX2o5VkhoYm1Ic3ZtWWs0QjlwRS1FUHdRWHYxX2pUVkJQTHdlWG9ubGxUbGlUekU2SXBURFBLaml0Tl9hU2tycHBObnM4SkF4WG95b2dnbkNJNjdnR19IbnVvNzBjRkptN1BoNzN0RGEzN3Y0RVhvSllJSGhxMm1BLTBNcUp5NlBPdzN5VWx1OUcwM3N6d0xmVnpIcG9fS25QOEFYQzhqVWpWdzBZazVmQTBlaGo0c2x5MjJoM3RSYmdTdFNISzVvSmQzWjVCMTBaLU1FVjN4dG1VMEdQTml5X2ZPaXBPMmpNM2FyMGc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxNZm9XVFZCMmxEWm5BXzN2OHJZZ1Z4SGJzTTNMVVB2VGl6dXRvN2MybzRJV01HcVlvd3IwbEZtWnoxQ2w2VTdQWXFzMXpTVElwcjdkVy1WbE0zZHpqQTRSZ0xrcDYwYmMzVExwaEhHWG1HTGVlZUJVT3lUWmR2LTh3MjhIYmUwNmcxQkR3aGVfREtiSEVOd3lvZXNIRFIzdjFpa1BDNDFtdWZYWTg?oc=5</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1519,38 +1519,38 @@
         </is>
       </c>
       <c r="K20" s="1" t="n">
-        <v>46136.18237268519</v>
+        <v>46136.4569675926</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>High Level City Belgium Dutch</t>
+          <t>Local Town Maasmechelen Dutch (fallback)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>("Brussel" OR "Antwerpen" OR "Maastricht") AND (bom OR bommelding OR "verdacht pakket" OR "onbeheerd pakket" OR explosie OR schietpartij OR steekpartij OR liquidatie OR arrestatie)</t>
+          <t>("Maasmechelen" OR "Hasselt" OR "Lanaken")</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Verdachte opgepakt voor reeks diefstallen uit auto’s in Elsene: politie vindt 35 computers en tientallen rugzakken bij huiszoeking - HLN</t>
+          <t>Schachtentemmer (26) schuldig aan verkrachting, maar straf krijgt hij niet: “Niemand is erbij gebaat zijn toekomst te dwarsbomen” - HLN</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Suspect arrested for series of thefts from cars in Ixelles: police find 35 computers and dozens of backpacks during house search - HLN</t>
+          <t>Schachtentemmer (26) guilty of rape, but he will not be punished: “It is in no one's interest to thwart his future” - HLN</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Thu, 23 Apr 2026 13:12:42 GMT</t>
+          <t>Fri, 24 Apr 2026 08:05:43 GMT</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi-AFBVV95cUxOWlo1MENOaXVDdTlSNUIxb2dwR0ZHLXFZWlY1dnQtUjVRTTVXa3lLWUVFdUd6TldkUXE1eXRyYkE0QlVhdVo4d1VuZ0RqdERUYUtSejdkUEFRZDBwRXlmMk9mNEhPN2JJeUJSaW96ZTZhNHJNODVXZm1UX1B6MDFMZkV0LXVHSDQwanN5VnBrTnRGVm1Ud3d5NnZuMjV4MDluQ0o3dzRmU0lJZlFZY2pzckhJYVlrcXpWNGlHQkNYUmJ6NVRxVlQ1c2lMb2hJV2doeFA2VGJ2eWxqUUo0UHVoUHk2Ukk2aVVGcHRQS1NXdU9JUUUyd0o5Vg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi8gFBVV95cUxONDE4N2JJcEhyUHVnUVQxWmE0V3NmTUtzMll6cVFfeXotSnpRVUNMVkR3aDFxNEMzRk9DUGc3NFVteldRb1BMMW9Xblk3YnVXWXRrUjJmbWd0YW5xTDdRRXZ5NVUzczJ2UGpKeVhYWGJTUU1xeWNyT09IUzl6a2U1TE4yR2l0bDRGQk9IcWN2VkJjMEhOM2IzWWdDV0N2SFhCTmlERFY4VGZaZlU5QkFKOVpsQUh1R3phcG8wWnVsT2FrMlpNR1BUUVItQmcyMGhPUFduamtyeU1tb1pZSFBRRFYyV3FsdWI3a2UxVFA5OVAzdw?oc=5</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1574,38 +1574,38 @@
         </is>
       </c>
       <c r="K21" s="1" t="n">
-        <v>46135.55048611111</v>
+        <v>46136.33730324074</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>High Level City Belgium Dutch</t>
+          <t>Local Town Maasmechelen Dutch (fallback)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>("Brussel" OR "Antwerpen" OR "Maastricht") AND (bom OR bommelding OR "verdacht pakket" OR "onbeheerd pakket" OR explosie OR schietpartij OR steekpartij OR liquidatie OR arrestatie)</t>
+          <t>("Maasmechelen" OR "Hasselt" OR "Lanaken")</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Afscheid van Vic Van Aelst (78), strafpleiter van de ‘hopeloze gevallen’ - Knack</t>
+          <t>De koolmees koning, maar de pimpelmees rukt op: zo telde Hasselt tijdens Het Grote Vogelweekend - HLN</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Farewell to Vic Van Aelst (78), criminal lawyer of the 'hopeless cases' - Knack</t>
+          <t>The great tit is king, but the blue tit is advancing: this is how Hasselt counted during The Big Bird Weekend - HLN</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Thu, 23 Apr 2026 15:24:20 GMT</t>
+          <t>Fri, 24 Apr 2026 07:37:39 GMT</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxNb0J5ZXZDaE9IVkFLclBGdlkycGU2N24zZWl3RzV4OVNRRWhpd3NPWk9xSFZTNC1ZSmFzMDBXTEk0bDNBODdXcmI0UjFWNGRib1o5OGRoWEZCM2ZyUGxTQzlQX1BVTE1rYnE2NWZpMXpyWjRMYWlaWDhRWDNTMUp2Mndoam9mTFBmejdEdlhpU0hONWdacUFfUXZHZ2hsdjZ1ZUw1dDFB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxOVFJGMnE5SUJpUUtmX3FNekxqTEhxSGwxcy1qMENwaTd5MjBWYWlzTzM1ZS1uNVQxeEViMEJyNno0VV9wdXRRSHk4Skg0MHB3OWRsY0RZeEo1RWVlSXNkOFR1LWtBOVdpX0xoNTVkM0RFTmVGVDJWQVp6bk9YS1JhZ05pOXpyYl92NkdIU242NzgzTl9wTDlEYXRib0VxMERTOWZFQjVTLXFpOUhQSVN2djRBOEU1a3dDV3FveWZtY2hjWlJ2T2hoTGpn?oc=5</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1629,38 +1629,38 @@
         </is>
       </c>
       <c r="K22" s="1" t="n">
-        <v>46135.64189814815</v>
+        <v>46136.3178125</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>High Level City Belgium Dutch</t>
+          <t>Local Town Maasmechelen Dutch (fallback)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>("Brussel" OR "Antwerpen" OR "Maastricht") AND (bom OR bommelding OR "verdacht pakket" OR "onbeheerd pakket" OR explosie OR schietpartij OR steekpartij OR liquidatie OR arrestatie)</t>
+          <t>("Maasmechelen" OR "Hasselt" OR "Lanaken")</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Brandweer heeft stevige kluif aan “levensgevaarlijke” promostunt van rapper Drake - GVA</t>
+          <t>VOEDINGSWAREN IN DE SUIKERSTAD, MODESHOPPEN IN LEUVEN OF HASSELT: DAAR MOET WAT AAN GEDAAN WORDEN - De Gazet van Hoegaarden</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Fire brigade is having a tough time with "life-threatening" promotional stunt by rapper Drake - GVA</t>
+          <t>FOODS IN THE SUGAR CITY, FASHION SHOPPING IN LEUVEN OR HASSELT: SOMETHING NEEDS TO BE DONE ABOUT THEM - De Gazet van Hoegaarden</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Thu, 23 Apr 2026 19:36:18 GMT</t>
+          <t>Fri, 24 Apr 2026 13:18:06 GMT</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxORE5nWEZVNUM1MTFNWUZsOHdQVmZaSU93THpObnNnMHFWVjhwNU1GbnZnQUZWZzBlS0FLMmxHMXhhRFRCaEQ0RzFVdzBELUFybl90YkM1LTRKY05tUGY5M2E0a1dyck5rSUV5VU1xdzktckw5ZlJGLUp2WnVMMkczdWFKMFNEbGxqY0JDTzVSclVhWF9QOUwyTmd5c0M5REZLandVTHJqWWZ1cFA3YzJ3SHpheEtsQy1pNWtXcnA4VTdPdzlGcHpva3FBT0VqSm9aWHdqMTN3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxQSEdBM2dZQ2kwZC1HUF9NU2xNZVBod3FOekFTaUZtRTlTbktfR0Jkc3NfbUo4YVhnMGJWT0lCcEJ2bmkxa3J0WkpfRmFuSHBITk9YVnlKUUlfYjVjUUlRdjZ2cTB5MlVrdmp5YTBUM05FVi1sc2hVVlZrX2RUNFo0LXl1WlJaSEtOMURWQlpJWEFlWTRkdGRmVGJ6WjlxYnRYSWJQcHpJbUF2b2lHbVJUZzNuRGJsdXplaW1sLUxfdEdNQ25VX2VsNEpBbmhSZkktSGZHNjBPMk4?oc=5</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1684,38 +1684,38 @@
         </is>
       </c>
       <c r="K23" s="1" t="n">
-        <v>46135.816875</v>
+        <v>46136.55423611111</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>High Level City Belgium Dutch</t>
+          <t>Local Town Maasmechelen Dutch (fallback)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>("Brussel" OR "Antwerpen" OR "Maastricht") AND (bom OR bommelding OR "verdacht pakket" OR "onbeheerd pakket" OR explosie OR schietpartij OR steekpartij OR liquidatie OR arrestatie)</t>
+          <t>("Maasmechelen" OR "Hasselt" OR "Lanaken")</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Rechtbank Brussel - Advocaat van medeverdachte Viktor Labin hekelt "schijnproces" - MSN</t>
+          <t>OPROEP. Wat vind jij van het schrappen van de buslijn tussen het station en de gevangenis in Hasselt? - HLN</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Brussels District Court - Lawyer of co-suspect Viktor Labin denounces "sham trial" - MSN</t>
+          <t>CALL. What do you think of the cancellation of the bus line between the station and the prison in Hasselt? - HLN</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Thu, 23 Apr 2026 18:45:10 GMT</t>
+          <t>Fri, 24 Apr 2026 07:53:38 GMT</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxNV3Q5NmM1bXBSYWIwSk9BRnc3NDk3YnNrQngwcDg2d2JMWUFSWlNWMTNTc0p1aVlZczlwTksxTDZOOEdlODByT2hKSENlcGpwWjl2NXZ1OVhhN2pFcF9iOUZkZkM2dVpvWGJOc0hnVXgtcFhnS2J2T0dtbFFXdXdDQ3FOSkJsOWNVTWxnbzBaU2RheDdXS2VOMDQ0Nl9oTnV1MXV2V2JxOElxdUFyWVlDdUY4MkJ1Vll4eHNjeUtGNFNaWE1GS3VRazlWS1U?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxOZ2ZVTzRuSTU2blZrT190SVE4Qm42TGlkbFV6S3pGMF83T0J6MkFNNlFFZGhPNlBPeTg1YUJYMU9aVzlnQjkxY0NJWUhwVmJPUkNoMWhSR0gyeF9HbHdlcDlMbGtmcWdjaGx0S0JNUWROSVFSd3Y5NzMzMXVqRk53SGtLOW1DM3g5eG5QdmYteTk2VlVZdVFKT01UMG1jM3VZRXNPemllVmNhekZvZkxJaXF0MWNRQURZTW40OHVPQ2dlZ1g5RGlPWkQ4b0FlRkJDMGc?oc=5</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1739,38 +1739,38 @@
         </is>
       </c>
       <c r="K24" s="1" t="n">
-        <v>46135.78136574074</v>
+        <v>46136.32891203704</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>High Level City Belgium Dutch</t>
+          <t>Local Town Maasmechelen Dutch (fallback)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>("Brussel" OR "Antwerpen" OR "Maastricht") AND (bom OR bommelding OR "verdacht pakket" OR "onbeheerd pakket" OR explosie OR schietpartij OR steekpartij OR liquidatie OR arrestatie)</t>
+          <t>("Maasmechelen" OR "Hasselt" OR "Lanaken")</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Duffel krijgt erkenning als Verkeersveilige Gemeente - Nieuwsblad</t>
+          <t>DERDE PROVINCIALE. Vijf degradanten gezocht, afscheid van boegbeelden en Juve aan het feest? - HBVL</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Duffel receives recognition as a Traffic Safe Municipality - Nieuwsblad</t>
+          <t>THIRD PROVINCIAL. Five relegates wanted, farewell to figureheads and Juve at the party? - HBVL</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Thu, 23 Apr 2026 22:45:00 GMT</t>
+          <t>Fri, 24 Apr 2026 10:48:36 GMT</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxOOUczOE5oMHF6RHRIc0gtOU8yTjlBRHk2Vm5LVlduTnl4UExEb3gwWGR1NThwbTh5TE5DNnJJR1Boa2cyTTl0ZERzbmlXcHpMeWYtUThxaHpCRTNEc0hhcnd5R3JnVzZGUkhMeUh1T3FCVC1JanZvX3IwamJTa3Fsc0IxaWpPX3Rxek10UXBaVDhteFFKYkktWFBUWWpad041QUVKb2pUUGR6eHlwbHpWUHB5NGZYckplVy0wN1VERVBub3ZLRlhPRA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxQNl9TYWtxam5hUm1qeVk5SWx3Z3preGVSMHI0aml5blF3ZVJLeXR2WUtPNWNOVGxTTC02TVMyLXhEVWk0TG8wdnF0OU0wd2Ruc1RtUldVVDg5MER6anlZWFF3Nm0xdkZQX2oyRGRFUGF5dUJjOVF4ODQ1ZG9zOTNOWDk4ZlFzemlwXzZWOWY3alAycGlrZTBWNGszUmJtYjh1QUZZSXNNWEVyVUVGcGZoUnV1STFhWW1yUHVURzNxWXphNWRTa3NNM0tMcDdPWjZrT044Ynd3?oc=5</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1794,38 +1794,38 @@
         </is>
       </c>
       <c r="K25" s="1" t="n">
-        <v>46135.94791666666</v>
+        <v>46136.45041666667</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>High Level City Belgium Dutch</t>
+          <t>Local Town Maasmechelen Dutch (fallback)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>("Brussel" OR "Antwerpen" OR "Maastricht") AND (bom OR bommelding OR "verdacht pakket" OR "onbeheerd pakket" OR explosie OR schietpartij OR steekpartij OR liquidatie OR arrestatie)</t>
+          <t>("Maasmechelen" OR "Hasselt" OR "Lanaken")</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Fietspad op ventweg krijgt asfaltlaag: verkeershinder in centrum Oud-Turnhout - Nieuwsblad</t>
+          <t>NATIONAAL VOETBAL. Voorzitterswissel, spits in ziekenhuis en feest in Hasselt en Pelt? - Nieuwsblad</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Cycle path on service road gets asphalt layer: traffic disruption in the center of Oud-Turnhout - Nieuwsblad</t>
+          <t>NATIONAL FOOTBALL. Change of chairman, striker in hospital and party in Hasselt and Pelt? - Nieuwsblad</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Thu, 23 Apr 2026 08:36:00 GMT</t>
+          <t>Fri, 24 Apr 2026 13:30:43 GMT</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxObWdBc2w0STRCLXg2OGRhb3BpZC1QVEpwRnlTVnoyaDgwYWxrQ3BTMV9fWGxJdll4U05YaTY0OV9pbDA0OUtxLTJKQzJaM0NWTVd2SWdlcXlEa21lZnlIUjhSSGpubXlXeVREQlZRQzdGa3g3OWctbEtLVHFnMHJxN2twT3h3NEdNei1famYxTW5qSmtuYWlDWjZ1VVRpYmc4ZlROM29yblNtWDNzaFR3UkJQbzJRdmxMRFZGNkRoRzNvekdETlBWdFR5RnQwcUFPb09JcElYQjQ5dW5NZFdQeUVVekl0NHpz?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxPR2pZYzRZS09jWTY4RWJtSWJjdldvUTF0amNfaExCQTJrMjNfVXlnVS13VmVid1ZZY2FmRF9ydXRjT2Qtd1FQZHBJeElQTWNrNDBSSWtpX2NuT2MxdjRBUWFQb1J0a1paOWFZWVo2OUVRSXI3UnlDVnlQR19pQnFOemxZbGVtNnlpYjNSMGRDdy1BVTJMeUVWSTRXQ012ZGpZY3pJaWRrUTBvTlNnZWV2TTZaR2tNSllOS0diUTh3dXBBYkxmTTBNU0swZ1NWYnZTUmRRQzdhVW9IUQ?oc=5</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1849,38 +1849,38 @@
         </is>
       </c>
       <c r="K26" s="1" t="n">
-        <v>46135.35833333333</v>
+        <v>46136.56299768519</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>High Level City Belgium English</t>
+          <t>Local Town Maasmechelen Dutch (fallback)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>("Brussels" OR "Antwerp" OR "Maastricht") AND (bomb OR explosion OR shooting OR stabbing OR "suspicious package" OR "bomb threat" OR "terror") AND -football AND -soccer AND -transfer</t>
+          <t>("Maasmechelen" OR "Hasselt" OR "Lanaken")</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>'Shocking, detached from reality': How is Brussels responding to latest drug explosions? - The Brussels Times</t>
+          <t>TWEEDE PROVINCIALE. ‘Langstzittende’ coach weg, wie zakt in 2A en wie pakt titel in 2B? - HBVL</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>'Shocking, detached from reality': How is Brussels responding to latest drug explosions? - The Brussels Times</t>
+          <t>SECOND PROVINCIAL. 'Longest-serving' coach gone, who will drop in 2A and who will take the title in 2B? - HBVL</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Thu, 23 Apr 2026 07:57:32 GMT</t>
+          <t>Fri, 24 Apr 2026 10:25:06 GMT</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxOZm1VTTFJZVZRODVscWNqUmlORVo0UUpsb0daWWVsTHYxZWV3UjlIYUVxNjhfYXJ1Tmd4ZlVFNGd3Q3l2aDM2eFZzcjY3V2VDeVdRWHQ4eVh1eFl2QV9NeV8yOVVUMkE3Q0xlQVU5QXpxdnJldTBhdnBkZWt0eW1Xb1ItbF9hN1c3SjBjUkFUOWNkYThTN3BFQWdTNWZXZG5VaXJLTjJpV25ISXZCSlNwOGdfNVFuc2ZRZUJPS0NB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxNS0JxNmJaRDZBSkx2X29uQk44MENFbkpoSUdXTzlKY3U3Z21Ic1hHV2l1akJ3bXB5dy02YklHSmlPdTluX2JnaEpyZ0FOdzlySldSMHd1MWZPc2g0ZzV3V3o2d1dZOUZnSm1SNnpLbF9fMmVYc1dPNE9BMGkyeDN6cU5HQVZodzJfNWl1N2UtSXJqT1dSUTE0OW9kMEcyamtrSlFoR0J1ZHNvT0gtQnppenduVXdTV3ZPeThOdWxMMmZpeWJZMGk5a3RhUlg?oc=5</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>en-GB</t>
+          <t>nl</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1900,42 +1900,42 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>BE:en</t>
+          <t>BE:nl</t>
         </is>
       </c>
       <c r="K27" s="1" t="n">
-        <v>46135.33162037037</v>
+        <v>46136.43409722222</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>High Level City Belgium English</t>
+          <t>Local Town Maasmechelen Dutch (fallback)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>("Brussels" OR "Antwerp" OR "Maastricht") AND (bomb OR explosion OR shooting OR stabbing OR "suspicious package" OR "bomb threat" OR "terror") AND -football AND -soccer AND -transfer</t>
+          <t>("Maasmechelen" OR "Hasselt" OR "Lanaken")</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Ahead of Passover, Israelis warned of increased threats worldwide amid war with Iran - MSN</t>
+          <t>Schachtentemmer (26) is schuldig aan verkrachting van schacht, maar hij krijgt geen straf - HBVL</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Ahead of Passover, Israelis warned of increased threats worldwide amid war with Iran - MSN</t>
+          <t>Schachtentemmer (26) is guilty of raping the shaft, but he receives no punishment - HBVL</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Thu, 23 Apr 2026 10:01:07 GMT</t>
+          <t>Fri, 24 Apr 2026 09:31:49 GMT</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxOY2JaRm1iNDFnNVQ4SW40STBUbnVTV3lYdW1RNW1TM083U2lfZk9KdHlwZXNKQ3dZU2lQRVhMSXNmT2hzbGFkc0tEdlg1ZGVUZEVpbW1zemd4NDJsSC0yblFqbUJ2UzdLQ0xyMTdFanB6UWlheDEwZ080ODdtczNSNTgtcmxJVzN2LUJEUFpxQjlGalhFTmFQajRRMHpjdTNFQVpnWGVmTWZSQWhBOXlWcXZ2RW9FamR5eWFQMDBWSDgxU1F1clVMRWVwVGI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxQekIydDF6bzczTVZ0R09VekxEMnVhSnAxcXo4Q3FjY0ZibmVpSHl2U3JWUUN3UWRPd0ROMFVpbEpJSUdfMU9GNVBGck52YWlrZ2J4bzlNcFpmMnk3NzRibTM0NGpqMGlqM0M1YWc5OFJoU1RjckFCb3JkbmowamVHRWVnblNibjFwd3dzSFRvZmNGRjFZclN0NmtUeHh2aHdYUE1vSUJPTjRiZXpWMmVwaExjdEhOdlZ3bWNobG1TMXpsZF9zWF9EeFd0a0FVSXZvYmp2YjMwVGJ0ZFE?oc=5</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>en-GB</t>
+          <t>nl</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -1955,42 +1955,42 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>BE:en</t>
+          <t>BE:nl</t>
         </is>
       </c>
       <c r="K28" s="1" t="n">
-        <v>46135.41744212963</v>
+        <v>46136.39709490741</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>High Level City Belgium French</t>
+          <t>Local Town Maasmechelen Dutch (fallback)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>("Bruxelles" OR "Anvers" OR "Maastricht") AND (bombe OR explosion OR fusillade OR agression OR couteau OR "colis suspect" OR "alerte à la bombe" OR attentat) AND -football AND -transfert</t>
+          <t>("Maasmechelen" OR "Hasselt" OR "Lanaken")</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Les Vingt-Sept se penchent sur leur clause d'assistance mutuelle - Boursorama</t>
+          <t>“Als de trein passeert, moet je er op springen”: voorzitter Alexander Verduyn en CEO Tom Vroman willen de kans op profvoetbal met beide handen grijpen nu SK Roeselare licentie op zak heeft - Nieuwsblad</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>The Twenty-Seven look at their mutual assistance clause - Boursorama</t>
+          <t>“When the train passes, you have to jump on it”: Chairman Alexander Verduyn and CEO Tom Vroman want to grab the opportunity for professional football with both hands now that SK Roeselare has a license - Nieuwsblad</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Thu, 23 Apr 2026 15:22:24 GMT</t>
+          <t>Fri, 24 Apr 2026 13:39:43 GMT</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi8gFBVV95cUxQOEpBM2VrZmJrLVlDVDItdFNHRWV2b0szbW9XN0VsM1VxVGtWQU5hc3ppTzVwTlhqNjBZazJTRXAzandMTzRHQXpMbDdyVGdlVGdSbUhlY1VDTnRhTS1BdGtmWllYeHlva1ZLell5dDZwamw5NTRKU1VzTFRrcGpOWVU5SGxjYnpybGk1c3BLSHhwcWU2aXVVN3pTYl96ODBHMzFmcDB3dGw4NjE3R0cwaTZOeE9ySnB2dmFJNzl3U2JOcFpsZER0MGYzRlZmaWZKdUhaVkhITjBVeW4xdDk5ZkJIVnRwNjBwYXhkSWJkWGFwd9IB8gFBVV95cUxQOEpBM2VrZmJrLVlDVDItdFNHRWV2b0szbW9XN0VsM1VxVGtWQU5hc3ppTzVwTlhqNjBZazJTRXAzandMTzRHQXpMbDdyVGdlVGdSbUhlY1VDTnRhTS1BdGtmWllYeHlva1ZLell5dDZwamw5NTRKU1VzTFRrcGpOWVU5SGxjYnpybGk1c3BLSHhwcWU2aXVVN3pTYl96ODBHMzFmcDB3dGw4NjE3R0cwaTZOeE9ySnB2dmFJNzl3U2JOcFpsZER0MGYzRlZmaWZKdUhaVkhITjBVeW4xdDk5ZkJIVnRwNjBwYXhkSWJkWGFwdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3wJBVV95cUxOdXNyc25ob0t0SGN4czhPcFlnTGlkd2ZpdUNPZ3RKT1AyUXl3RlNxN2tCb2trWjFBWGw5aFYwblZvOG1ScGdjNkd1bHdOdjBBQUU0UW5XUGd0b0Q4VHhtdjFjZy1sUmlVMklXR3FQREVJREtWcDVKSTltMGhoTG5iMGhqaGIxYWlvMFdUQ3phM0ZsbW9MZEEwX3kwemZ6bTl6a1p4dUhsNHNWY1NVNklabmtSamdXV0V0U3ZXeG5Ub29fVVRDWGVmWUowcVBhMUxpT3VMWVhHWC1BcDdwTkJMZXVpbzVRdnJPb0VBYWhQUklTVWw2elNFSlBrODRRRDN4djNHenltVmRPOThmX3ZTb2w1VTBMV0ZmLUtHTU5YM1BObWszZUJJUUoxUzhJNTcxYk9Hd3NQUy1ReUtuUkF2dVdtUXpUd2c0MmJ4bVY1Zll4VWRaR0ozQzh1THpsczQ?oc=5</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -2000,7 +2000,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>fr</t>
+          <t>nl</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2010,42 +2010,42 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>BE:fr</t>
+          <t>BE:nl</t>
         </is>
       </c>
       <c r="K29" s="1" t="n">
-        <v>46135.64055555555</v>
+        <v>46136.56924768518</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>High Level City Belgium French</t>
+          <t>Village Wertheim (fallback)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>("Bruxelles" OR "Anvers" OR "Maastricht") AND (bombe OR explosion OR fusillade OR agression OR couteau OR "colis suspect" OR "alerte à la bombe" OR attentat) AND -football AND -transfert</t>
+          <t>("Wertheim Village" OR "Wertheim") AND (shopping OR outlet OR luxury OR retail OR news)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Luxembourg : l’Europe fédérale entre explosion et radicalisation - reinformation.tv</t>
+          <t>UF’s president search nears finish as dean vacancies remain - The Florida Times-Union</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Luxembourg: federal Europe between explosion and radicalization - reinformation.tv</t>
+          <t>UF’s president search nears finish as dean vacancies remain - The Florida Times-Union</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Thu, 23 Apr 2026 15:34:00 GMT</t>
+          <t>Fri, 24 Apr 2026 09:32:53 GMT</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE10MjdST0NjZjdOSHRIZFdFSFN1bTZiUHlEU0hVempIcEh4UXVkYXoyNjdWTDREbm1SUzc1dUp5N2dlRVh1X1diXzNUY0NhcS05RGNTTHFCZ0FzVV8zUXVDY3ktci13UHU2Rk81Wm5MX3J1c2VDdVQ5Y3ZHTjJYWWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxPam5QSjhXYlR5SV9OVUZNWXlqd0VwYThOelA4eGxZaDRFdERhVVN3amgwbFhyUmdGRS1acW5WN1drQ2ZTanFHc1J2bFhNc1otM2VZNGlwcFpjVzZidFNQWjhpWXJjeHdwSElIRG5TdXd2N1lPN0hRb3lJQ2VWTDZwRlM3VmpmZGQ0a3JST2dob0MyVHRIXzZpVDRkbEhaajhTSTN4TEpNaEhuQ0Y4QUVXeGFmWE9FcnBhMmxsc0ExaFVNamo5VDlTWHpJaTVabnltdzFXOXNmRXF6UUFxeFhXSWxycjZGaU8y?oc=5</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2055,52 +2055,52 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>fr</t>
+          <t>en-GB</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>BE:fr</t>
+          <t>GB:en</t>
         </is>
       </c>
       <c r="K30" s="1" t="n">
-        <v>46135.64861111111</v>
+        <v>46136.39783564815</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>High Level City Belgium French</t>
+          <t>Local Town Ingolstadt German</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>("Bruxelles" OR "Anvers" OR "Maastricht") AND (bombe OR explosion OR fusillade OR agression OR couteau OR "colis suspect" OR "alerte à la bombe" OR attentat) AND -football AND -transfert</t>
+          <t>("Ingolstadt") AND (Protest OR Bombe OR Bombendrohung OR Explosion OR Schießerei OR Polizei OR Evakuierung OR Terrorverdacht) AND -Audi AND -Auto AND -Wetter</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Attentats de Madrid : Ancien ministre espagnol accuse le Maroc - moroccomail.fr</t>
+          <t>Schwerpunktkontrolle nächste Woche: Polizei überprüft Zweiräder im Stadtgebiet - Augsburger Allgemeine</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Madrid attacks: Former Spanish minister accuses Morocco - moroccomail.fr</t>
+          <t>Focus check next week: Police check two-wheelers in the city area - Augsburger Allgemeine</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Thu, 23 Apr 2026 13:17:50 GMT</t>
+          <t>Fri, 24 Apr 2026 09:50:35 GMT</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxOc2N1M1ZjUDQ5eU4xem0yN0JBSWwzWmtnTGNiLUgtTjZEcUY3MTBEVzB6QVk3SDFheEQtRi14X3M1UzFBMS0yTlJ0eUV0NzhjMjhNMUVTTXkyRGNQZEV2WXVqeU9vNWJoenlsbTlaejd0bi0wTW10czN2VnM4UHJqMmdCZzFZVXlUam5STkNXMVV0ZXN4dW9hNTRoaXp5NzlSZkNnWHhkLXlEVTNLdTlOR2ZYZnrSAbQBQVVfeXFMTnNjdTNWY1A0OXlOMXptMjdCQUlsM1prZ0xjYi1ILU42RHFGNzEwRFcwekFZN0gxYXhELUYteF9zNVMxQTEtMk5SdHlFdDc4YzI4TTFFU015MkRjUGRFdll1anlPbzViaHp5bG05Wno3dG4tME1tdHMzdlZzOFByajJnQmcxWVV5VGpuUk5DVzFVdGVzeHVvYTU0aGl6eTc5UmZDZ1h4ZC15RFUzS3U5TkdmWGZ6?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxQeTFudjEzbzlIc2FBRnhNeURUM0loOHNiU3c4TXJVQkdmS3VVcUppcjlRY2RBVEg5REQxdEhQc3FlcmRFTUtfeEhVNFpZVzF2UWFta0N2QjNUNTFDNXE1akducTh6N1dUajhuaWpjM0dMdG8wLXB0emdiYk4tRGdjRTZDblFmSjE5VmJJRGxETUZZUGtTR0ZWT1lHZzdleHBELUI5dnZscUJycWo5SEx2X3JIZXRaOUtXU0twVldld0trcnRNOThNeTlOV3lZTHFF?oc=5</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2110,52 +2110,52 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>fr</t>
+          <t>de</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>BE:fr</t>
+          <t>DE:de</t>
         </is>
       </c>
       <c r="K31" s="1" t="n">
-        <v>46135.55405092592</v>
+        <v>46136.41012731481</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Village Wertheim (fallback)</t>
+          <t>Local Town Ingolstadt German</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>("Wertheim Village" OR "Wertheim") AND (shopping OR outlet OR luxury OR retail OR news)</t>
+          <t>("Ingolstadt") AND (Protest OR Bombe OR Bombendrohung OR Explosion OR Schießerei OR Polizei OR Evakuierung OR Terrorverdacht) AND -Audi AND -Auto AND -Wetter</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Copter Rescues Teen Stuck In Mud At Wertheim National Refuge - MSN</t>
+          <t>Polizeibekannter 20-Jähriger sorgt auch bei Schrobenhausen für Aufregung - Pfaffenhofen Today</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Copter Rescues Teen Stuck In Mud At Wertheim National Refuge - MSN</t>
+          <t>20-year-old known to police also causes excitement in Schrobenhausen - Pfaffenhofen Today</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Thu, 23 Apr 2026 10:52:35 GMT</t>
+          <t>Fri, 24 Apr 2026 11:06:11 GMT</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2wJBVV95cUxOekU3Zm9CZzZkVzYtM1BUR0ZBeExSSHBNenQ4X0Y4NnJPYXk5RUlkQ1IwVFROS3VtWUVJZUlaRTJPMUVKZ1VuQ0FsUlowd0QtNEhTX1NZNGNRbVN4T2xQalZYS0RVazc1SU11OUZuRzVlWnFzeGI1dnJySEx0eVdHVDcwdW03MEliSm5jcHVGTGJ5MFd1ZnRkNnAyRzhvMkVGZUlYVWoteE9JVHA3MG5kZVNZVXhzdjRfQjZtQTRYb2ZFdDhIUGtBRGZ6dGhjTlNTaDZvLTJTRDJyNGpNOVk4M2I1R2Y2Q3NMb1ZmVlRtQzJoRHZ6UFh0Y3BqS2F6c0JDT2pXMENiR2pqYTBRdmVNVmxhNWRwY1hnTWVYQUtJaVBtUGdvaHJFS3RmTVNSR19Md0ZrNER0V2JNYUVhRE9KSmtmQlZqZktNVDNaRWFTRGFhVWpDcm9kWTBMUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiakFVX3lxTE8tdC05VmZvU2ZXT1ZVTWVGZEt3UHhVTFh0UkpubU1DcGtrUlpDTUlEVmY3WUVoaTJoUUl4NV95dGptMkN2cThycWJQaHZKVFAybTNpV2xwN0JsMmY0ejdCV2c5OURkVDdiYUE?oc=5</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2165,52 +2165,52 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>en-GB</t>
+          <t>de</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>GB:en</t>
+          <t>DE:de</t>
         </is>
       </c>
       <c r="K32" s="1" t="n">
-        <v>46135.45318287037</v>
+        <v>46136.46262731482</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Village Wertheim (fallback)</t>
+          <t>Local Town Ingolstadt German</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>("Wertheim Village" OR "Wertheim") AND (shopping OR outlet OR luxury OR retail OR news)</t>
+          <t>("Ingolstadt") AND (Protest OR Bombe OR Bombendrohung OR Explosion OR Schießerei OR Polizei OR Evakuierung OR Terrorverdacht) AND -Audi AND -Auto AND -Wetter</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Florida State Hosts Inaugural Legacy Tea Honoring Women of FSU - Florida State University News</t>
+          <t>Crash auf der B13 bei Baar-Ebenhausen: Zwei Verletzte, zwei geschrottete Autos - Pfaffenhofen Today</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Florida State Hosts Inaugural Legacy Tea Honoring Women of FSU - Florida State University News</t>
+          <t>Crash on the B13 near Baar-Ebenhausen: Two injured, two wrecked cars - Pfaffenhofen Today</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Thu, 23 Apr 2026 15:56:11 GMT</t>
+          <t>Fri, 24 Apr 2026 11:50:11 GMT</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxQQldHZEd0N1VVNmdySWpHZlgweGduV3JucGRlSG1pRm5SMV96N2VkWDdDNzZwOW5kaG9Fa3hSd21wd1pPNlFiOU16UVNCd00wVVdZTWoxY0pjOWZzMm5Ud2pmMV9lNWNKYjh4cHg0eVpOcnlaTW1Lak8yYXBTVUcwRUdjdHQ3UTBTZkNEYkt5bW5DaTM4LWNVYTM1ejd1YjNCdkNwS3RJSzBqVVRjTlB5YmZR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMia0FVX3lxTE9fTEJXS28tWjNkTjJYYl9VdW5idkZaeFhlN2FvUldGWjBERklkMk1kZkNOaE5faHNpcURybWtPUUdGb25uWmVublQ4RHRvUENNZl9RYVlqRWFqdXJiS1ppSHdQYk91aTlvQnhB?oc=5</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2220,52 +2220,52 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>en-GB</t>
+          <t>de</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>GB:en</t>
+          <t>DE:de</t>
         </is>
       </c>
       <c r="K33" s="1" t="n">
-        <v>46135.6640162037</v>
+        <v>46136.49318287037</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Village Wertheim (fallback)</t>
+          <t>Village Ingolstadt (fallback)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>("Wertheim Village" OR "Wertheim") AND (shopping OR outlet OR luxury OR retail OR news)</t>
+          <t>("Ingolstadt Village" OR "Ingolstadt") AND (shopping OR outlet OR luxury OR retail OR news)</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Elena Rybakina Closes WTA Ranking Gap After Stuttgart Title Win - readers.id</t>
+          <t>Audi Confirms Fall 2026 A2 e-tron Start as Ingolstadt Sheds Q2 - The EV Report</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Elena Rybakina Closes WTA Ranking Gap After Stuttgart Title Win - readers.id</t>
+          <t>Audi Confirms Fall 2026 A2 e-tron Start as Ingolstadt Sheds Q2 - The EV Report</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Thu, 23 Apr 2026 13:41:37 GMT</t>
+          <t>Fri, 24 Apr 2026 10:00:00 GMT</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE1SSnZMYkRFTGJSVVY0MWdmN2VFWlJ2QjA1N3Q3QllNUTd4cGFNYTdkUkhlN3BHQkhYVDZINjE5WUx6eU41WXZSMUdLLVhsdUFKSTJkUUFsMG9NRlFRTjhPcFBHaENQXzZKb19WVmxrWXg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxNbXZZTDFITjk5WXN4TEp5OWJDT3NXQXgtRDlkeTRRamRxbnVXeUllVU40czc3OUtaWWxBdEF6Nmh2VVdOcUhTS2k1SVhnSlp1c1QyRW9HeTJqMVhzMzNzRWdCLWhrNVBVa2gtcldfTGRHQWtnbEdWQlNyQk9VcnRkZEhtaGJURkh6RFVWQzJTcw?oc=5</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2289,38 +2289,38 @@
         </is>
       </c>
       <c r="K34" s="1" t="n">
-        <v>46135.57056712963</v>
+        <v>46136.41666666666</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Local Town Ingolstadt German</t>
+          <t>Village Ingolstadt (fallback)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>("Ingolstadt") AND (Protest OR Bombe OR Bombendrohung OR Explosion OR Schießerei OR Polizei OR Evakuierung OR Terrorverdacht) AND -Audi AND -Auto AND -Wetter</t>
+          <t>("Ingolstadt Village" OR "Ingolstadt") AND (shopping OR outlet OR luxury OR retail OR news)</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>20-Jähriger löst erneut Polizeieinsatz aus und wird in Klinik eingewiesen - Augsburger Allgemeine</t>
+          <t>Audi revamps production, ends A1 and Q2 lines - Just Auto</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>20-year-old triggers police operation again and is admitted to clinic - Augsburger Allgemeine</t>
+          <t>Audi revamps production, ends A1 and Q2 lines - Just Auto</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Fri, 24 Apr 2026 05:53:03 GMT</t>
+          <t>Fri, 24 Apr 2026 13:14:15 GMT</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi8AFBVV95cUxQM0pZcDJzNWwtTEszSmY0bkFZR29PbnJWSG1ta25HNExkR3lDQko0cTl3MVdMdHY3S3k5bG1HaHlpbTNPTkhVc0hsYkFhRGRkNTdZVUZuNTZYNDVBSml6dmRoVG9nS25PXzRiNzAySmxHcFZuNlRTQ1FycWJEem5ybGt4RUdlNUt4WERwNjdFNno0X2pXUnNkRWZhdFZUcUJKQ2N4YXl1MmVHLTVfN3Q5SlpMei1MMHczZnc5V3ZHQkRtbWo0NzBjeVlPajA2RjNuRDB5TDFuMGVucmk5N2NFMWxpTEV5RkFfMFFQTmx6Q2M?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiZkFVX3lxTE1NZTZQZFYxaUJ6dUZ6Smp5OUt6SUhXdXVHSndUTDJfbWdKeXF3Q0FHZ3lKdEZRczljbkdPUGJtRVNBd1lwei11OS1yb200cHNKSzc1YWRIcTAtZU1NejFJWUdMWEozdw?oc=5</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2330,52 +2330,52 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>de</t>
+          <t>en-GB</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>DE:de</t>
+          <t>GB:en</t>
         </is>
       </c>
       <c r="K35" s="1" t="n">
-        <v>46136.24517361111</v>
+        <v>46136.5515625</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Local Town Ingolstadt German</t>
+          <t>High Level City UK Ireland</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>("Ingolstadt") AND (Protest OR Bombe OR Bombendrohung OR Explosion OR Schießerei OR Polizei OR Evakuierung OR Terrorverdacht) AND -Audi AND -Auto AND -Wetter</t>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" OR "Protest" OR "blockade" )</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Autofahrer übersieht rote Ampel – Fünfjähriger reagiert in letzter Sekunde - Augsburger Allgemeine</t>
+          <t>Waymo 'driverless' taxi ploughs into London crime scene after double stabbing - London Evening Standard</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Driver misses red light – five-year-old reacts at the last second - Augsburger Allgemeine</t>
+          <t>Waymo 'driverless' taxi ploughs into London crime scene after double stabbing - London Evening Standard</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Thu, 23 Apr 2026 08:04:41 GMT</t>
+          <t>Fri, 24 Apr 2026 08:02:33 GMT</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxNTVU0N3hIR2laQWgzV2FNUUxEc0d4S1dMWUhNajI3X2JWOUYwWERRaWhEd2l5Y2F6d3A1eHNfUVlOQ3hUeUVzNUVWVHg0aTBsRUc4Y3c1REVUbTZ6Vi00MXk4NDBoRDVWRlpISnZoZ1p0NW5SUkFwclliZ2lCYmxRX1NwelByQXZrdGVTVm9xU2ZtWkRubGthVXB0Q0RRVm5CZFRHeTNTRWRmWDlDNWx3cUNrSjBHV2FWVWJkNVFVXzdUWGw0UHJQOTY2MW1sUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxQY2Fna3ZCSC00NTcwc3l1bGxNVnVLbU9Sb0U5bml6NkZyaU1Ga19SMkVIWGwxaGJIaVdiRW5VcGtnaWVOZFYwTHFsZm95Y0FTWFY0ejN0N1ZodTlETzN6dGxlR3dpaTFjQjRhbGFlQTd4bW1kak9iVER1VGxWRlExS25wbndmNVFhVktWYjY5M2p2aGVHOTlrcFRJeDEzdS1OOHNkanNRNHVYckhZQjlRRVgzZ2ZSWHc?oc=5</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2385,52 +2385,52 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>de</t>
+          <t>en-GB</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>DE:de</t>
+          <t>GB:en</t>
         </is>
       </c>
       <c r="K36" s="1" t="n">
-        <v>46135.33658564815</v>
+        <v>46136.33510416667</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Village Ingolstadt (fallback)</t>
+          <t>High Level City UK Ireland</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>("Ingolstadt Village" OR "Ingolstadt") AND (shopping OR outlet OR luxury OR retail OR news)</t>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" OR "Protest" OR "blockade" )</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Audi strengthens production network: integrated production and new fully electric model in Ingolstadt - Audi MediaCenter</t>
+          <t>WAYMO TEST VEHICLE CRASHES INTO POLICE CORDON DURING LONDON STABBING INVESTIGATION - PHTM</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Audi strengthens production network: integrated production and new fully electric model in Ingolstadt - Audi MediaCenter</t>
+          <t>WAYMO TEST VEHICLE CRASHES INTO POLICE CORDON DURING LONDON STABBING INVESTIGATION - PHTM</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Thu, 23 Apr 2026 08:00:00 GMT</t>
+          <t>Fri, 24 Apr 2026 09:50:26 GMT</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi7gFBVV95cUxNX2t6WjkzNmRzMHZBNGVFNm5xQ0hnUjZkU3EzMGxRbG1WaHgtal9EaVByRkxEOUNRMHVjUHpZSXJMZnV1LTRvNi1CQmlaQlByZVAzeWFmM0cxMTMyZ29peWUtZzVCdDY3TG1qelpBS3RuZDRlRS05X3RheXAyUUJYVWd4bG5seHB0TmhSaEpIYlVqR0lHNDExMHEzQXhsNG0xU0RzcFBYcG5aTksxMFhMNkk2SEhPdnRIMzc3YlZENEdvaXZ6YWFZaG9PODFhQ3lmZjRnWkd0a1FMbm1Xb3owR282YVJnOFM4ZVlMNVRR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxObUg4RWs1NWFkaXBtNFp0NlZLMU81OGw1MmJvMkVaRmUzS3ZvTGlrTTdKSEF4OU9xWmlqTEFnRmRyajV0WlY0Z09lWkxveGR1XzVxeV9SOHpqRW44dTNPRzNJN1VpcFN1dWZQLWtyZEZCa2g5SnVoc3ZDd1dzQ2trTTZ4ZE84SnlLZFpYQVJPV2ZzTVpNZ2RyWTI4V05FNjN3STZ1MTdHaEVEQ0R3cEpJaFdmMXNfaHREX0RscW1hamNrYW8?oc=5</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2454,38 +2454,38 @@
         </is>
       </c>
       <c r="K37" s="1" t="n">
-        <v>46135.33333333334</v>
+        <v>46136.41002314815</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Village Ingolstadt (fallback)</t>
+          <t>High Level City UK Ireland</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>("Ingolstadt Village" OR "Ingolstadt") AND (shopping OR outlet OR luxury OR retail OR news)</t>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" OR "Protest" OR "blockade" )</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Gabriel Bortoleto visits Audi in Ingolstadt - Audi MediaCenter</t>
+          <t>Two men charged after 27-year-old died in south London shooting - London Now</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Gabriel Bortoleto visits Audi in Ingolstadt - Audi MediaCenter</t>
+          <t>Two men charged after 27-year-old died in south London shooting - London Now</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Thu, 23 Apr 2026 16:40:00 GMT</t>
+          <t>Fri, 24 Apr 2026 08:05:12 GMT</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxQUzRvb2FuZ0pQdGE2MWpnemk5WDVYV2VFUGY2QnU4aDdUWUxGaUt5THZhRzZ3OVBYQUVkMFdGb3VTenJ4UWxqUzRKNGRmcDNvWUtWb0ltTDJtV0JyQ3F3b0VNVGptSVZxQVVKcGJMOHgxaUlCS1ZIV3BMZGxPVTlsZXhrMnFFUWpOWmg5cU9wM1RhRDZpb245c0wtREFCU2Noa2c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxOOTdNNTNsam5kcjF6cHlSR1NhZGdsTEM4blA1RU93ZXliTVhvV2tfU1pwMVN6djFsRHdvY19uMGRhclFhdVJvanNVMmE3OGRmSHZVSXBMU3YwU05nV0MtRlFhRkNqX3RZSVRabWFLcFZrSEtXT3hQeWRsU2hXU3VrV2ZZRFlKNmhTbEhVZGtJdnJ2QUdwMkRBRlcydUE?oc=5</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2509,38 +2509,38 @@
         </is>
       </c>
       <c r="K38" s="1" t="n">
-        <v>46135.69444444445</v>
+        <v>46136.33694444445</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Village Ingolstadt (fallback)</t>
+          <t>High Level City UK Ireland</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>("Ingolstadt Village" OR "Ingolstadt") AND (shopping OR outlet OR luxury OR retail OR news)</t>
+          <t>("Oxford" OR "Bicester" OR "Oxfordshire" OR "London" OR "UK" OR "England" OR "Britain") AND ("protest" OR "demonstration" OR "blockade" OR "strike" OR "march" OR "rally" OR "civil unrest" OR "disorder" OR "dispersal order" OR "anti-social behaviour" OR "flash mob" OR "social media gathering" OR "link-up") AND -sport AND -football</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Audi fans will either be really excited or sorely disappointed with its new performance car - MSN</t>
+          <t>The London Underground will be hit by four days of strikes this week - Time Out Worldwide</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Audi fans will either be really excited or sorely disappointed with its new performance car - MSN</t>
+          <t>The London Underground will be hit by four days of strikes this week - Time Out Worldwide</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Fri, 24 Apr 2026 02:46:54 GMT</t>
+          <t>Fri, 24 Apr 2026 07:27:00 GMT</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilgNBVV95cUxPY0htLVN4RVpUcktLNGFZOHNXMnJ6YlNKWV8wMWd1SGZoeXRmbk9OYTBSRkxxZms5Z0JMaEQwd3gtcW9BcTBqUm1sZUVTY2tEazNjWTdEdklPN2FwQU1pZXRObjByUlFONHNmc2EtY1lCZk1oVmxmLXVMT0lsSzllZlQ0TXNLb3Q3aTMxaHJNWklOZy1uT0h4d3FCNXZzRDZTSENjeVV4Z05sc0x2WXVKRTNRdW5HbjBIcHhYQ21PdU5pQWdKOXVtUlVyM1pWTDBKWDNKM1kySnoyNHVlZkRzZ0huVWxXRDdBVlJjMzZvRWRWczFCUFRkOXpERHBadW1SUjRrdXd4cTZoY1M2STVETDJpekdmV28xUHlBVEZkUzI5dFNHZUNXY2k2UjFFaTd6UmxwRmNheS1CTGdRT2Y4S2x4MkVvcjFsbmhFTVREM3J3SFd6bmE5MHM3Sjh4MFp0M0l1dHRMXzJLckl1Ui1kMHRnVTdnRnRoQWw3bG0wZERQdF91RE0zb0FBZHlNbWl2VXRMNzZ3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijAJBVV95cUxQZTZ1aU9ULWZDREhGLWtWQUVXNk9mVVN2ek84MkhkUWJDbUhRMzBlZHUxc3lvYThnS1E0X1BUMkhHY0h4Qk5GZnJaeGpKclRJdmJoSGdocEVaQTQ3aFRIdEFMbEdMalVsc0VNaXZUb1VXWEZSc2xqNGxTQ2NfdEpWQXdvWTEzV04zTlgzeWVKYWxGWjNMU2ZGRnhtbUtLdnNwUXYycS1oVlJQV195VTZtRHloX3EwdS11WEdXMEZ5Y1dMNE41VElUc3VwMUhZWFZmb0hXQVRIeFM1aERvbFByWUpZeHVpRzVFdmRwT2ZMUXh0anpFSjBCbXk1aDl2TTAxV2x0a3NSVGEyZlZp?oc=5</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2564,38 +2564,38 @@
         </is>
       </c>
       <c r="K39" s="1" t="n">
-        <v>46136.11590277778</v>
+        <v>46136.31041666667</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Village Las Rozas La Roca (fallback)</t>
+          <t>High Level City UK Ireland</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>("Las Rozas Village" OR "La Roca Village" OR "Las Rozas" OR "La Roca") AND (shopping OR outlet OR luxury OR retail OR news)</t>
+          <t>("Oxford" OR "Bicester" OR "Oxfordshire" OR "London" OR "UK" OR "England" OR "Britain") AND ("protest" OR "demonstration" OR "blockade" OR "strike" OR "march" OR "rally" OR "civil unrest" OR "disorder" OR "dispersal order" OR "anti-social behaviour" OR "flash mob" OR "social media gathering" OR "link-up") AND -sport AND -football</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>St. Bernards celebrates 10,000 robotic surgeries with student hands-on demonstration - K8 News | Jonesboro, Arkansas</t>
+          <t>Which Tube lines are running as second 24-hour strike hits London? - London Evening Standard</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>St. Bernards celebrates 10,000 robotic surgeries with student hands-on demonstration - K8 News | Jonesboro, Arkansas</t>
+          <t>Which Tube lines are running as second 24-hour strike hits London? - London Evening Standard</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Thu, 23 Apr 2026 21:44:00 GMT</t>
+          <t>Fri, 24 Apr 2026 12:13:39 GMT</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxPMEVEWTkwT2xBUkRmVE1ZbzBtaTZzUWJPX29YNEl4Q0p0cTVfZWF6OUk2WXhkdjNNcmRMZm9zZF9pd1hnOFdWcTFuaTBNSEkxTkNMSEtPOC1QdV9WMkwycW01WGxmRHVxSzRtaDdqVXRZNjROQkQ4UXlGaXVVWlNKdHg5TWxjZHZJMWFCTFFYbHJPdmdva2FSSkNyZTdUb1VocERaNXY3eEYtOWtIRzk0MEROTDJfeXlRZHB1aGJPblVKazNrV0VwYmIwc9IBywFBVV95cUxPMEVEWTkwT2xBUkRmVE1ZbzBtaTZzUWJPX29YNEl4Q0p0cTVfZWF6OUk2WXhkdjNNcmRMZm9zZF9pd1hnOFdWcTFuaTBNSEkxTkNMSEtPOC1QdV9WMkwycW01WGxmRHVxSzRtaDdqVXRZNjROQkQ4UXlGaXVVWlNKdHg5TWxjZHZJMWFCTFFYbHJPdmdva2FSSkNyZTdUb1VocERaNXY3eEYtOWtIRzk0MEROTDJfeXlRZHB1aGJPblVKazNrV0VwYmIwcw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxPWXBNTFRkWXpLOXE3MXhLWFR5NkhaN2xoOEtXMGdVUFB0N0JQS0dncWt2SFdsaVp5bVF5Q3I5dXNIcXVnWXM4WnFfc0dva2RodzVSNkFNRDNQSk0yR25oS3F3QVZJdk1JSDhVMndmREpjTmFJeUhNNWRvVTJ1dTN4YjI3czlEVXBRRzhCZGpEUkxZVUpTc0RZNmxKUQ?oc=5</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2619,38 +2619,38 @@
         </is>
       </c>
       <c r="K40" s="1" t="n">
-        <v>46135.90555555555</v>
+        <v>46136.50947916666</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Village Bicester Kildare</t>
+          <t>High Level City UK Ireland</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>("Bicester Village" OR "Kildare Village" OR "Bicester outlet" OR "Kildare outlet")</t>
+          <t>("Oxford" OR "Bicester" OR "Oxfordshire" OR "London" OR "UK" OR "England" OR "Britain") AND ("protest" OR "demonstration" OR "blockade" OR "strike" OR "march" OR "rally" OR "civil unrest" OR "disorder" OR "dispersal order" OR "anti-social behaviour" OR "flash mob" OR "social media gathering" OR "link-up") AND -sport AND -football</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Entire Kildare Village Owned by Ryanair Founder on Sale for €20 million - Nova.ie</t>
+          <t>London's latest Tube strike revealed to be union's least effective in YEARS - GB News</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Entire Kildare Village Owned by Ryanair Founder on Sale for €20 million - Nova.ie</t>
+          <t>London's latest Tube strike revealed to be union's least effective in YEARS - GB News</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Thu, 23 Apr 2026 10:21:14 GMT</t>
+          <t>Fri, 24 Apr 2026 11:30:38 GMT</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxQNThTZTZDcDAzQnpFMllJX09mcEYtcnR4b1lxS1JIWVF5LXBEM0pIQzB1TzBRZW1Ed3ZmU3BTMGU1dndBcGZmcmFYS0RCVXhoT3ZkaEhtcW5mVi1JSkpKX2dxLTZyUndYSk9hWUpINTg4QzNIWWF3LUo4Z29RX3NSeXBPOUljSzBkcVFfQmZQQVlYZWFsQXozQk05NllUY1lw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTE9IRjhHVnEwY3JnSm1PdFZOdmdtT05jaDZzVVhvcnJZSjlPZTFKMkZsWi10Y2ZKVDBPSXBOdWR1NDltOFhIdmFDcTJFOXRpVmg1R3RZdTBEU0llZENYOXJuYkF2eTQtdEpzOERwcWc0WDZlV002?oc=5</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2674,38 +2674,38 @@
         </is>
       </c>
       <c r="K41" s="1" t="n">
-        <v>46135.43141203704</v>
+        <v>46136.47960648148</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>High Level City UK Ireland</t>
+          <t>High Level City Italy Italian</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" OR "Protest" OR "blockade" )</t>
+          <t>("Milano" OR "Bologna") AND (protesta OR manifestazione OR corteo OR sciopero OR blocco OR presidio OR "sit-in") AND -calcio AND -moda AND -"settimana della moda" AND -Serie AND -mercato</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Waymo 'driverless' taxi ploughs into London crime scene after double stabbing - London Evening Standard</t>
+          <t>In arrivo uno sciopero Atm a Milano: gli orari di metro, bus e tram (e le fasce di garanzia) - MilanoToday</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Waymo 'driverless' taxi ploughs into London crime scene after double stabbing - London Evening Standard</t>
+          <t>An ATM strike is coming to Milan: metro, bus and tram timetables (and guarantee periods) - MilanoToday</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Fri, 24 Apr 2026 06:32:43 GMT</t>
+          <t>Fri, 24 Apr 2026 07:43:02 GMT</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxQY2Fna3ZCSC00NTcwc3l1bGxNVnVLbU9Sb0U5bml6NkZyaU1Ga19SMkVIWGwxaGJIaVdiRW5VcGtnaWVOZFYwTHFsZm95Y0FTWFY0ejN0N1ZodTlETzN6dGxlR3dpaTFjQjRhbGFlQTd4bW1kak9iVER1VGxWRlExS25wbndmNVFhVktWYjY5M2p2aGVHOTlrcFRJeDEzdS1OOHNkanNRNHVYckhZQjlRRVgzZ2ZSWHc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxOR183OEFPOERIUUd4RGF3bjFWNVZ4bF9ZWmVhSy1QT1ZwaFliT3N5MFpqaHJGNzBHdGdGWkJlNzJSZUtpeWUwWGlqNGFlXzB5UEhqNXRQZXhWVHM3U2VPejg5TzliY2djV2ZGM2JUYWVNVFFiT3BnWlEwVHhjdVBPZFZoUGlZOVk?oc=5</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2715,52 +2715,52 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>en-GB</t>
+          <t>it</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>GB:en</t>
+          <t>IT:it</t>
         </is>
       </c>
       <c r="K42" s="1" t="n">
-        <v>46136.27271990741</v>
+        <v>46136.32155092592</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>High Level City UK Ireland</t>
+          <t>High Level City Italy Italian</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" OR "Protest" OR "blockade" )</t>
+          <t>("Milano" OR "Bologna") AND (protesta OR manifestazione OR corteo OR sciopero OR blocco OR presidio OR "sit-in") AND -calcio AND -moda AND -"settimana della moda" AND -Serie AND -mercato</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Two men in their 20s in hospital after stabbing — what we know so far - London Now</t>
+          <t>25 Aprile, manifestazione in centro e cortei nei quartieri di Milano. Le strade chiuse - MilanoToday</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Two men in their 20s in hospital after stabbing — what we know so far - London Now</t>
+          <t>April 25th, demonstration in the center and processions in the neighborhoods of Milan. The closed roads - MilanoToday</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Thu, 23 Apr 2026 07:32:47 GMT</t>
+          <t>Fri, 24 Apr 2026 11:46:05 GMT</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxONUFFZGRTSnd2bGtZOU1WQUxtWGxubjlHalJVZjJnNW84TWRBUGxNaXhZSXdwNURpeF9vNXcxNDJ5T3pldDZWSkctclFKZFFDNU9iWnV4bUk5UDZlWGZuRXVzLWV4cF9hRmJobTBLNDFfR3RfRm9Fc0w3WUNZa2djVVhMWWNRdWtEbzJHTWItR3BPNmNlUkRiSERfcUVwb2JC?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxNRUF5TnZsWFNzZF9aelJvRUhJRE9xYUMtUG5jeThyNjA1RThjQi0ycThwVm9aQnhwVW5xeUxqQ05iT1lvWDBjTENIQnhYVkJZNFdZZ0xqMFVMUHdpb2c1d1pRWFJ3d3VCSExUMW9qT09GemF2Y0g5SjNIZm5nNW1sWlZiaFgxMjBpc2c?oc=5</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2770,52 +2770,52 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>en-GB</t>
+          <t>it</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>GB:en</t>
+          <t>IT:it</t>
         </is>
       </c>
       <c r="K43" s="1" t="n">
-        <v>46135.31443287037</v>
+        <v>46136.49033564814</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>High Level City UK Ireland</t>
+          <t>High Level City Italy Italian</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" OR "Protest" OR "blockade" )</t>
+          <t>("Milano" OR "Bologna") AND (protesta OR manifestazione OR corteo OR sciopero OR blocco OR presidio OR "sit-in") AND -calcio AND -moda AND -"settimana della moda" AND -Serie AND -mercato</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Four murder suspects arrested after man, 24, stabbed to death in Leyton - Guardian Series</t>
+          <t>Daniela Fumarola interviene a nome dei sindacati confederali alla manifestazione del 25 aprile a Milano - Cisl Scuola</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Four murder suspects arrested after man, 24, stabbed to death in Leyton - Guardian Series</t>
+          <t>Daniela Fumarola speaks on behalf of the confederal trade unions at the demonstration on 25 April in Milan - Cisl Scuola</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Thu, 23 Apr 2026 13:21:34 GMT</t>
+          <t>Fri, 24 Apr 2026 10:23:00 GMT</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxOSDBVM2Vka3c4QkdQWGU1M3ZHQkNUMks4RjhYYmhCR21MTWRHTmFpcjE4N0p1ZXFBV0JpNGhSMF80a0pvYmdxdHI0WDNEVmpSTmRGVklnTnVYVVRpMms3TnpvcHgyWHFVUVJuRE1pOEtKWVIzRHQ4d3QteE45ZGFhSWFPMDVGMk1qaWotNWpuQmpOOUhWbm05a1Uta0o5YzF5UG5MWVlvUnA4ZGs?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi5AFBVV95cUxQRFkwWjhSOTVvMWJXWmk2aTc1cnkteUlhZXp6WjF4LUFfZnB0QnJLbVRNcFNFNms4am40aFlQOHdpNHVPX1VPanpoQW9QNG1icWpYRjRQbGhobzU3UzFUbFp2X1hCY0VoOG4zWmtDZTF5dC02MGZFRlpvWTk2ZC1RLXpYU0Riamt3RHczdjZkZU1MOUlYU3VjSDVTcEMwb1lHOGVaaHBQUjVlRkhDbVJhQjdmRVRJTXpzODloOVdDM2xJODgxUy1DRWZkcElfa1RyQTl5ZDJkc014NWg4OWxFakNMbVQ?oc=5</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2825,52 +2825,52 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>en-GB</t>
+          <t>it</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>GB:en</t>
+          <t>IT:it</t>
         </is>
       </c>
       <c r="K44" s="1" t="n">
-        <v>46135.55664351852</v>
+        <v>46136.43263888889</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>High Level City UK Ireland</t>
+          <t>High Level City Italy Italian</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" OR "Protest" OR "blockade" )</t>
+          <t>("Milano" OR "Bologna") AND (protesta OR manifestazione OR corteo OR sciopero OR blocco OR presidio OR "sit-in") AND -calcio AND -moda AND -"settimana della moda" AND -Serie AND -mercato</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Man missed daughter's wedding after 'bomb in luggage' gag - RTE.ie</t>
+          <t>Festa il 25 aprile, fra cortei, spettacoli e concerti - vivimilano.corriere.it</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Man missed daughter's wedding after 'bomb in luggage' gag - RTE.ie</t>
+          <t>Celebration on April 25th, with parades, shows and concerts - vivimilano.corriere.it</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Thu, 23 Apr 2026 18:00:45 GMT</t>
+          <t>Fri, 24 Apr 2026 12:12:45 GMT</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE5zTnM0OExJTV9DOUhVOHhSMWg1ZTIyUXh4Zy1PazZYbEpnX3hYMVoxSXpnTHdSWnRMcE9ILWFmYVYwU21ldWpzZFZVWldlcTUzWmE4RXdmZDYtUTN4eVVOVzhMQV9XbjQ1QWY0bVNXQnd5bnpBQmNGMQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxQWkF2NzVFZ2F6cDA5ejhlOXRublVwZGtUMFpfYmNSU293eFI2UGpRWDVKSmxKY2RrMDdFM3JfQTVoa0hOdGpiOThRYjQ3aTdsamIxcnpKeWZWUTFzR1lwWnpINUhaUzdNdG5XN2VmXzRKQ2d5a3B0aEkzNThsd3Fzd0pmQ2NTUjViNGhaTWpZc2I4Z3ZLTzkxN0Q1bTE0bUQ3QVgyUkNGZDgtQVVKaUZ1TG1n?oc=5</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -2880,52 +2880,52 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>en-GB</t>
+          <t>it</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>GB:en</t>
+          <t>IT:it</t>
         </is>
       </c>
       <c r="K45" s="1" t="n">
-        <v>46135.75052083333</v>
+        <v>46136.50885416667</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>High Level City UK Ireland</t>
+          <t>High Level City Italy Italian</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" OR "Protest" OR "blockade" )</t>
+          <t>("Milano" OR "Bologna") AND (protesta OR manifestazione OR corteo OR sciopero OR blocco OR presidio OR "sit-in") AND -calcio AND -moda AND -"settimana della moda" AND -Serie AND -mercato</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>London stabbing victim recounts random attack, long road to recovery - London Free Press</t>
+          <t>Mezzi Atm a Milano in servizio nonostante sciopero - Bresciaoggi</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>London stabbing victim recounts random attack, long road to recovery - London Free Press</t>
+          <t>ATM vehicles in service in Milan despite strike - Bresciaoggi</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Thu, 23 Apr 2026 11:09:11 GMT</t>
+          <t>Fri, 24 Apr 2026 08:12:58 GMT</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxOWm5MZndaZWowTXYzdUlsR0g0UjJvc2hpUGlsRlkydWczTWNCeEsxYlpTa3E1SW8yTGR2OHRjZVNYT1kteDNGSGcwT3RVVXYzMVpPMzZLbnRySHVFbkhxMThvOHhwUDdSbkRzNW5wU3Zzcy1HN21kYzJHRzByWDYtWG1PdThueG9CS20wbW1Semg0c2pxN2U5TVVvYmFBUVl6TVdDTjdB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxPZzNoTFlVeGVramZiNjMyTVozTXZRVnlLNWY2NjZfVEhJd0FoaE1YcTRBRWZfX1RYZEktMFktbkVUdXQ5X2ZKeGRGWjE0cUJoU2JHS0VxMjU2bWtGR1hIbGk1bXFTYzZhWWdVQTY2bzA0QmpvdkF1ZDhCaW5jVHZVZ0VnVUhidkRFUDh4aEFqTU5MOWJTQ0xEcFZkMFJ5T0VFT3JnR3VGVUpzdFnSAasBQVVfeXFMT2czaExZVXhla2pmYjYzMk1aM012UVZ5SzVmNjY2X1RISXdBaGhNWHE0QUVmX19UWGRJLTBZLW5FVHV0OV9mSnhkRloxNHFCaFNiR0tFcTI1Nm1rRkdYSGxpNW1xU2M2YVlnVUE2Nm8wNEJqb3ZBdWQ4QmluY1R2VWdFZ1VIYnZERVA4eGhBak1OTDliU0NMRHBWZDBSeU9FRU9yZ0d1RlVKc3RZ?oc=5</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -2935,52 +2935,52 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>en-GB</t>
+          <t>it</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>GB:en</t>
+          <t>IT:it</t>
         </is>
       </c>
       <c r="K46" s="1" t="n">
-        <v>46135.46471064815</v>
+        <v>46136.34233796296</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>High Level City UK Ireland</t>
+          <t>High Level City Italy Italian</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" OR "Protest" OR "blockade" )</t>
+          <t>("Milano" OR "Bologna") AND (protesta OR manifestazione OR corteo OR sciopero OR blocco OR presidio OR "sit-in") AND -calcio AND -moda AND -"settimana della moda" AND -Serie AND -mercato</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>LIVE updates as high street closed for second day after man stabbed to death - London Now</t>
+          <t>Sciopero proclamato da sindacato Confial - GazzettadiMilano.it</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LIVE updates as high street closed for second day after man stabbed to death - London Now</t>
+          <t>Strike proclaimed by the Confial union - GazzettadiMilano.it</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Fri, 24 Apr 2026 06:25:41 GMT</t>
+          <t>Fri, 24 Apr 2026 07:38:55 GMT</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxOcUZsbDdIdU1PWnA0RHhVRkxGd1BiZmFTVlBfQ1drZEx1TmoyOHd2MXY4cm5abVFXM2Q3SEVtQ1Q5NHY2OV9fa1d5Snh2SkxZOGxGUkNVWHpmN3RkZE0tcTFBVUFXYzlJRFU5RnNUbzlqelVKYjVCQTZud1N1cGI2bl9oc180SC1tUEt0UndsakRqUENu?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTFBXdldWRHg4NS1SOFdTWVRyeV9tWUF5al9uNkFvbGhiUEdjRjJhUnlCbnlPMU5vNFNiTGZuRkVBaGNRQVpIWjh5UGpkQXhmcTBzVXVpNG5JSWpRNEktVzVEMXZ1SUgwNUNndU4yMDIwUzR3Ul9CRFhWVFFXMWQ?oc=5</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -2990,1011 +2990,21 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>en-GB</t>
+          <t>it</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>GB:en</t>
+          <t>IT:it</t>
         </is>
       </c>
       <c r="K47" s="1" t="n">
-        <v>46136.26783564815</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>High Level City UK Ireland</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" OR "Protest" OR "blockade" )</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Young man stabbed to death after 'altercation' in east London street - London Evening Standard</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>Young man stabbed to death after 'altercation' in east London street - London Evening Standard</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>Thu, 23 Apr 2026 14:35:48 GMT</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxPVjByNlJaUHd5cnBrTkhXaEozdDVoX0MzajZBRDc0Vy1KOFJabVlQa09ESlhIYWdmT3dlcWE4N0k3UnNUQU1ZUFFicmx5NUxJWlNSdi1zQWtYaW5VTll4Y1pDN1R1M2Z2emFIYkw1UVJwMndpeG5xSzlvUXc4cDVJQWVMV05STUpQ?oc=5</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>google_rss</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>en-GB</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>GB</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>GB:en</t>
-        </is>
-      </c>
-      <c r="K48" s="1" t="n">
-        <v>46135.60819444444</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>High Level City UK Ireland</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" OR "Protest" OR "blockade" )</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Four men arrested on suspicion of murder after fatal early morning stabbing - London Now</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>Four men arrested on suspicion of murder after fatal early morning stabbing - London Now</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>Thu, 23 Apr 2026 12:41:22 GMT</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxQeWlkVGYzQWN5bWJoLXo4dW9ycTRtUWdJRUllcjd6dUJYOENXeUp0ODl5Mm1ZRFMzajNPS1ZJbWlfVV96SVY0di1FbUFSU3ZKelFZd0VGVlEwTmk1eGV6anNyMmtuanpMTXVMUHprWWdMb0lXVXR3S200UFB2Y0dIZU80ZnZQRXMxY0hkQ0VhR0o2T1l5aGNBZ2k3dDhaOXJOazJFMA?oc=5</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>google_rss</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>en-GB</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>GB</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>GB:en</t>
-        </is>
-      </c>
-      <c r="K49" s="1" t="n">
-        <v>46135.52872685185</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>High Level City UK Ireland</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" OR "Protest" OR "blockade" )</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Man, 27, arrested after double stabbing on busy high street - London Now</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>Man, 27, arrested after double stabbing on busy high street - London Now</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>Thu, 23 Apr 2026 09:29:30 GMT</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxNbUhVeHhLbnM4MDBfNzM1dy0wSVdUd1IwcDhWakxEQXpTWklGMGFuN1A4VXB4a2lNcHA1bDdKWGNkQzVKUjRHRXhMN0FOdFVYTnhSYVVoUGxZY25IX05XSlhDOVVOZl96MV9pM0VrR1doMEY4Zllld3liMmc5cUIxSno1UTZua3g2RkhIYzdIc2wzMy1pcVE?oc=5</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>google_rss</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>en-GB</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>GB</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>GB:en</t>
-        </is>
-      </c>
-      <c r="K50" s="1" t="n">
-        <v>46135.39548611111</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>High Level City UK Ireland</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" OR "Protest" OR "blockade" )</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Watch: Iran War Protest Turns Bloody, Multiple Stabbed In London Chaos - The Times of India</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>Watch: Iran War Protest Turns Bloody, Multiple Stabbed In London Chaos - The Times of India</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>Thu, 23 Apr 2026 16:24:13 GMT</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxPMnJZQmNwZHNuWWVxdTJuRUhwbEFBYkJIWUNHc1ZWYWFFbW5qQXlEM1dZWmFOYklVUjI2YnhiLW1uclNmXzdOd3R3MVEwN19GSWFQTTk2OHVNaWQ5VkU4bElxQTZWVnlxalZYZGlTMmhWMFlUem9iQjVkWU44cVF6R2dKa1ByUkZLMFI3Z1h6TVdzVzc3RlNkLUJKZGZESE04dksyMzRhYWppdWhJZG15amxJUFVFekpHT0Y1LVFidEhJNFNTc0p4WF9lWmREdVlZX3lVYk1PVElvakt4RkZNcDUwQdIB6AFBVV95cUxQaWlLb1gzY0RHNFctS3BJaVRDYkJfS1hpSzQ0V0JkdlpOanRGQjRoX0VnQjhLM29KYzFGQ0oxVUZzWXNTNlF3WXI2Rkc4US1OakNqWXgxclVlY3F2VlBKRjh6Wkw2OF85QnpsZ2JpZXNBNHBfQ2xmRmdVOThqZ01HUWNVb2w1N0ZlNE5jdDNKVHFNQ2V6VDFucDBiLW96aDI4MlZ3X2NKYWtHa3VMczJIbUJuQzlSWFBjU250QTFXTXp4WnRxOXNrNExubEtmeHlDRjNKOFNKdmxKeE9SdXpCbUU4NkdfaHBN?oc=5</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>google_rss</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>en-GB</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>GB</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>GB:en</t>
-        </is>
-      </c>
-      <c r="K51" s="1" t="n">
-        <v>46135.6834837963</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>High Level City UK Ireland</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>("Oxford" OR "Bicester" OR "Oxfordshire" OR "London" OR "UK" OR "England" OR "Britain") AND ("protest" OR "demonstration" OR "blockade" OR "strike" OR "march" OR "rally" OR "civil unrest" OR "disorder" OR "dispersal order" OR "anti-social behaviour" OR "flash mob" OR "social media gathering" OR "link-up") AND -sport AND -football</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>London faces more disruption as second 24-hour tube strike begins - The Guardian</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>London faces more disruption as second 24-hour tube strike begins - The Guardian</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>Thu, 23 Apr 2026 09:49:00 GMT</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxPU2t0THp6YV8zT1IxUEpHTXg3WS1DMWVoODZMeWgtWU9CNTF5b05zRDdqZFBERV81Y1I0Y3VFRUZZVzk3dHVXanVUZGtDSjE5aG90cmZXcTUxX2JJQlNmSGlzTjJCWWhXcnl3czRra0pZa1lBYTBGZ2dUN0I2M05EZzJwZ0JMYzBxX3VoY05rdU9NcjY4aHFIWDJMUVRYT2Ztc3pYaHBGQXZsazlLcHNNMXpzZw?oc=5</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>google_rss</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>en-GB</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>GB</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>GB:en</t>
-        </is>
-      </c>
-      <c r="K52" s="1" t="n">
-        <v>46135.40902777778</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>High Level City UK Ireland</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>("Oxford" OR "Bicester" OR "Oxfordshire" OR "London" OR "UK" OR "England" OR "Britain") AND ("protest" OR "demonstration" OR "blockade" OR "strike" OR "march" OR "rally" OR "civil unrest" OR "disorder" OR "dispersal order" OR "anti-social behaviour" OR "flash mob" OR "social media gathering" OR "link-up") AND -sport AND -football</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>UK and France strike new £662m small boats deal - BBC</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>UK and France strike new £662m small boats deal - BBC</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>Thu, 23 Apr 2026 16:02:34 GMT</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE5STXNmVW1yQXhqVWlNS1dZOFhlRk81STdUNUdua0NvNFF3X0MxMXJqWFJ6aVBWNDNTWUcwUDltSksyRXROb1EwbW5QZXIzWXpTU0FsVFdteWhHQQ?oc=5</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>google_rss</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>en-GB</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>GB</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>GB:en</t>
-        </is>
-      </c>
-      <c r="K53" s="1" t="n">
-        <v>46135.66844907407</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>High Level City UK Ireland</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>("Oxford" OR "Bicester" OR "Oxfordshire" OR "London" OR "UK" OR "England" OR "Britain") AND ("protest" OR "demonstration" OR "blockade" OR "strike" OR "march" OR "rally" OR "civil unrest" OR "disorder" OR "dispersal order" OR "anti-social behaviour" OR "flash mob" OR "social media gathering" OR "link-up") AND -sport AND -football</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>London buses strike today — all we know so far about routes and impact - Yahoo News UK</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>London buses strike today — all we know so far about routes and impact - Yahoo News UK</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>Fri, 24 Apr 2026 04:00:00 GMT</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMie0FVX3lxTFBNRlBBUmpGUjdOU1lZMnVwRWVlU0I3V1BPTDhqSGo1c29mV0ttNlVlTnVEbWV5VmFveVlvZWdUczhXLUYwSXRMV0wyVWd6ZHV0dF8wMlhqQTVjaHc4ZDVERHZrREZLUVZZcGlxbDNBUlAxQjRZeTl4T1J2OA?oc=5</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>google_rss</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>en-GB</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>GB</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>GB:en</t>
-        </is>
-      </c>
-      <c r="K54" s="1" t="n">
-        <v>46136.16666666666</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>High Level City UK Ireland</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>("Oxford" OR "Bicester" OR "Oxfordshire" OR "London" OR "UK" OR "England" OR "Britain") AND ("protest" OR "demonstration" OR "blockade" OR "strike" OR "march" OR "rally" OR "civil unrest" OR "disorder" OR "dispersal order" OR "anti-social behaviour" OR "flash mob" OR "social media gathering" OR "link-up") AND -sport AND -football</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>The London Underground will be hit by four days of strikes this week - Time Out Worldwide</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>The London Underground will be hit by four days of strikes this week - Time Out Worldwide</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>Thu, 23 Apr 2026 07:19:00 GMT</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMijAJBVV95cUxQZTZ1aU9ULWZDREhGLWtWQUVXNk9mVVN2ek84MkhkUWJDbUhRMzBlZHUxc3lvYThnS1E0X1BUMkhHY0h4Qk5GZnJaeGpKclRJdmJoSGdocEVaQTQ3aFRIdEFMbEdMalVsc0VNaXZUb1VXWEZSc2xqNGxTQ2NfdEpWQXdvWTEzV04zTlgzeWVKYWxGWjNMU2ZGRnhtbUtLdnNwUXYycS1oVlJQV195VTZtRHloX3EwdS11WEdXMEZ5Y1dMNE41VElUc3VwMUhZWFZmb0hXQVRIeFM1aERvbFByWUpZeHVpRzVFdmRwT2ZMUXh0anpFSjBCbXk1aDl2TTAxV2x0a3NSVGEyZlZp?oc=5</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>google_rss</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>en-GB</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>GB</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>GB:en</t>
-        </is>
-      </c>
-      <c r="K55" s="1" t="n">
-        <v>46135.30486111111</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>High Level City UK Ireland</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>("Oxford" OR "Bicester" OR "Oxfordshire" OR "London" OR "UK" OR "England" OR "Britain") AND ("protest" OR "demonstration" OR "blockade" OR "strike" OR "march" OR "rally" OR "civil unrest" OR "disorder" OR "dispersal order" OR "anti-social behaviour" OR "flash mob" OR "social media gathering" OR "link-up") AND -sport AND -football</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Protestor stabbed at anti-war demo in Downing Street - thecanary.co</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>Protestor stabbed at anti-war demo in Downing Street - thecanary.co</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>Thu, 23 Apr 2026 13:40:30 GMT</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxOZkxvek5hak40dWMyd3lLMUZOcGpiWWlGZ3FTbWNSRVVqYVZFZmdUQmVtclJYV1M4RGFwZUE1LWhiNDAySy01S3BDS1BJdE9ZNWYyUDFfdE4zNUkxRDBBUkMzeEhPM3ZRQ0VyRkFzQUdNalBGM25nTWZ2QUppc1JYaGdTNDExU28?oc=5</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>google_rss</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>en-GB</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>GB</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>GB:en</t>
-        </is>
-      </c>
-      <c r="K56" s="1" t="n">
-        <v>46135.56979166667</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>High Level City UK Ireland</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>("Oxford" OR "Bicester" OR "Oxfordshire" OR "London" OR "UK" OR "England" OR "Britain") AND ("protest" OR "demonstration" OR "blockade" OR "strike" OR "march" OR "rally" OR "civil unrest" OR "disorder" OR "dispersal order" OR "anti-social behaviour" OR "flash mob" OR "social media gathering" OR "link-up") AND -sport AND -football</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Active Travel: London Underground strike sees capital’s busiest cycling day of 2026 - Highways News</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>Active Travel: London Underground strike sees capital’s busiest cycling day of 2026 - Highways News</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>Thu, 23 Apr 2026 10:49:12 GMT</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxOZ1lBYzRPNzhyOGI5MmJoOURTOEFkZ0Y1UTdnTXlmNEVGU3V0LU1wQ2hWZ2JoSDUwVGd6bU5LWDVnVE9UNHNJZXBJWWpjNVNRdUxteXEwZGZSUVpheE4tTmxPMUlxYXpVcnU5UGdoNU50SXlCUUpHczVvMHRnZHlXMWpwLXlFejdOWDdaVUktZnJKT1ZyZmYtSGUtbzVsYmVuMEhDNHY5V1lMSy1E?oc=5</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>google_rss</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>en-GB</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>GB</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>GB:en</t>
-        </is>
-      </c>
-      <c r="K57" s="1" t="n">
-        <v>46135.45083333334</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>High Level City Italy Italian</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>("Milano" OR "Bologna") AND (protesta OR manifestazione OR corteo OR sciopero OR blocco OR presidio OR "sit-in") AND -calcio AND -moda AND -"settimana della moda" AND -Serie AND -mercato</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>In arrivo uno sciopero Atm a Milano: gli orari di metro, bus e tram (e le fasce di garanzia) - MilanoToday</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>An ATM strike is coming to Milan: metro, bus and tram timetables (and guarantee periods) - MilanoToday</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>Fri, 24 Apr 2026 04:41:53 GMT</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxOR183OEFPOERIUUd4RGF3bjFWNVZ4bF9ZWmVhSy1QT1ZwaFliT3N5MFpqaHJGNzBHdGdGWkJlNzJSZUtpeWUwWGlqNGFlXzB5UEhqNXRQZXhWVHM3U2VPejg5TzliY2djV2ZGM2JUYWVNVFFiT3BnWlEwVHhjdVBPZFZoUGlZOVk?oc=5</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>google_rss</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>it</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>IT</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>IT:it</t>
-        </is>
-      </c>
-      <c r="K58" s="1" t="n">
-        <v>46136.19575231482</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>High Level City Italy Italian</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>("Milano" OR "Bologna") AND (protesta OR manifestazione OR corteo OR sciopero OR blocco OR presidio OR "sit-in") AND -calcio AND -moda AND -"settimana della moda" AND -Serie AND -mercato</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>25 aprile a Bologna, il programma tra cerimonie istituzionali e concerti. Corteo da piazza dell’Unità - Il Resto del Carlino</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>April 25th in Bologna, the program includes institutional ceremonies and concerts. Procession from Piazza dell'Unità - Il Resto del Carlino</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>Thu, 23 Apr 2026 17:09:10 GMT</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxQN00tQVZDd1BiN2hGcXJaVF84NEhWX2Q2VVlWNmpCRlVvSnN2ODc4RXRCYUsxMXppbGF2ZzczSDZmaTk1T1J0a3p6TDJVaV9PYzd1c0M0eWNscDFyTTRFYkktdENyTWpHUGVjNUpJemsxZjZ1UUpwSlNJU2tPNEhpQTJhQnQzdF9uekN6bmozZm8?oc=5</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>google_rss</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>it</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>IT</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>IT:it</t>
-        </is>
-      </c>
-      <c r="K59" s="1" t="n">
-        <v>46135.71469907407</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>High Level City Italy Italian</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>("Milano" OR "Bologna") AND (protesta OR manifestazione OR corteo OR sciopero OR blocco OR presidio OR "sit-in") AND -calcio AND -moda AND -"settimana della moda" AND -Serie AND -mercato</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Atm, domani a Milano sciopero in programma dalle 8.45 alle 15 - ANSA</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>Atm, strike scheduled for tomorrow in Milan from 8.45am to 3pm - ANSA</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>Thu, 23 Apr 2026 16:20:43 GMT</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMi6wFBVV95cUxNeXJDY0FJRU0wc1Z0VDRXMnVDY3Qtb3lBQnEwRzJ0OG5jajFRVjk4WTB4UUdGWjB4cERma0M3TEVYOHFSY0dja2xPMlJsRlUyMjJhUUtTTVFYQWlHMWthaGQ3QXpEYlRSMmowc1p0bVNabzZRNjhxRHdWTG1wZW96SjFqVUlQX0dwRG1QOTd4UXNkWjFNN1hBdHVDUzRtdkU4b2dwY2dzRzFjLU1OdC1HR20xTlY5VlJxTG5sbnY4cU5idDJ2STAteWduTUZuWXcxOGJrTjIxRklZX3ducXdKVUk1eU5Ma2U0UFFV0gHrAUFVX3lxTE15ckNjQUlFTTBzVnRUNFcydUNjdC1veUFCcTBHMnQ4bmNqMVFWOThZMHhRR0ZaMHhwRGZrQzdMRVg4cVJjR2NrbE8yUmxGVTIyMmFRS1NNUVhBaUcxa2FoZDdBekRiVFIyajBzWnRtU1pvNlE2OHFEd1ZMbXBlb3pKMWpVSVBfR3BEbVA5N3hRc2RaMU03WEF0dUNTNG12RThvZ3BjZ3NHMWMtTU50LUdHbTFOVjlWUnFMbmxudjhxTmJ0MnZJMC15Z25NRm5ZdzE4YmtOMjFGSVlfd25xd0pVSTV5TkxrZTRQUVU?oc=5</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>google_rss</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>it</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>IT</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>IT:it</t>
-        </is>
-      </c>
-      <c r="K60" s="1" t="n">
-        <v>46135.68105324074</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>High Level City Italy Italian</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>("Milano" OR "Bologna") AND (protesta OR manifestazione OR corteo OR sciopero OR blocco OR presidio OR "sit-in") AND -calcio AND -moda AND -"settimana della moda" AND -Serie AND -mercato</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Summit dei Patriots a Milano: le posizioni della Lega spaccano la destra - LA7</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>Patriots summit in Milan: the League's positions split the right - LA7</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>Thu, 23 Apr 2026 20:29:33 GMT</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxPWFFVY2hqendid09UTHlabWROMGtIZWp3WGxtXzBBZ1EwQzU0VFFRV1NMS09aRGVJYkhzYzRDTVA5NjhMRU1nT09HcXJSWHJiWFphaU8xMnNZMGN0MUhkdUpXSVJVbXplN0VydS14N3V4NGxnOFlMblB2c2hBX0pJMzF0bGVleDlZR1Q0YTMycDFtcDNjRGMzX3dITHNoMlZoOGFMMUFIM2tiY0tZQzU4SmxkX2NyeGp2REVSQUZoWThHQ3owbFHSAcsBQVVfeXFMTlU0WU9TTkNBcjRyLTJIZUg3N2hpMEZXZ2xKTjlNVWk2U05pYy1YM3o4ZVlrMG9SUXdFbUF4Nm9XaUJpYVhqWDl3LUg2R0dlMUN0TGVYWlJpT0dFNmw0NUdCZFBUXzViZkZMYjRMcWVOUjJPdkZIbTVKSlZ5YnJoTW5UbjltZEMtUGJNSmhVZnQ0ZUxIb2FTYWN0ekN3WXc0MXFIRG9JRVJwbkxienhzcU1ZbmVFYUwxMVZmUDFwSlNUQ2dVa3RlWXlVV1E?oc=5</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>google_rss</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>it</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>IT</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>IT:it</t>
-        </is>
-      </c>
-      <c r="K61" s="1" t="n">
-        <v>46135.85385416666</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>High Level City Italy Italian</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>("Milano" OR "Bologna") AND (protesta OR manifestazione OR corteo OR sciopero OR blocco OR presidio OR "sit-in") AND -calcio AND -moda AND -"settimana della moda" AND -Serie AND -mercato</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>25 aprile: Coordinamento pace, non porteremo tensioni in piazza Milano - L'Arena</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>April 25: Peace coordination, we will not bring tension to Piazza Milano - L'Arena</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>Thu, 23 Apr 2026 20:13:43 GMT</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxOcC1kWWtZWUg3MXVmalM0bG9hSDlMdmNQWnphamhoMlVnbzZoeXA2N0dlOTB2blp0SGRZMnBPd3o3eHk1Y2lSZTlEZmtrYW5EcXhMZ0hlX3pzUnUzYWQ3dWxKN1Vqblo2UHFWak1yajlqNk5jWWQwWDlSbzVRWlJESHlNZGs2YnBMb3B1R2hzOTBiRVVQRldEUkU4cnpyMkdFUVBEUnNpaFpuWmJXQkwySEViQXgwYWVp0gG4AUFVX3lxTE5wLWRZa1lZSDcxdWZqUzRsb2FIOUx2Y1BaemFqaGgyVWdvNmh5cDY3R2U5MHZuWnRIZFkycE93ejd4eTVjaVJlOURma2thbkRxeExnSGVfenNSdTNhZDd1bEo3VWpuWjZQcVZqTXJqOWo2TmNZZDBYOVJvNVFaUkRIeU1kazZicExvcHVHaHM5MGJFVVBGV0RSRThyenIyR0VRUERSc2loWm5aYldCTDJIRWJBeDBhZWk?oc=5</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>google_rss</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>it</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>IT</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>IT:it</t>
-        </is>
-      </c>
-      <c r="K62" s="1" t="n">
-        <v>46135.8428587963</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>High Level City Italy Italian</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>("Milano" OR "Bologna") AND (protesta OR manifestazione OR corteo OR sciopero OR blocco OR presidio OR "sit-in") AND -calcio AND -moda AND -"settimana della moda" AND -Serie AND -mercato</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Arriva un "maggio "nero" per i trasporti: il calendario di tutti gli scioperi del mese - Moveo by Telepass</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>A "black" May is coming for transport: the calendar of all the strikes of the month - Moveo by Telepass</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>Thu, 23 Apr 2026 13:36:34 GMT</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTE9lZDdSVmxUMGtWV1dKOGxfa2hEX1kxTjFMTkJVREhYcDJOdl9EYlp4SU9tcWFISk1McVFIMGtCT1luWVlqZUxCbm1XUG5vNWZMTTNGQ3Mwelg3eUVL?oc=5</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>google_rss</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>it</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>IT</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>IT:it</t>
-        </is>
-      </c>
-      <c r="K63" s="1" t="n">
-        <v>46135.56706018518</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>High Level City Italy Italian</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>("Milano" OR "Bologna") AND (protesta OR manifestazione OR corteo OR sciopero OR blocco OR presidio OR "sit-in") AND -calcio AND -moda AND -"settimana della moda" AND -Serie AND -mercato</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Il corteo apre il Primo Maggio . Poi contest musicale e teatro - Il Giorno</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>The procession opens on May Day. Then music and theater contest - Il Giorno</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>Thu, 23 Apr 2026 08:49:42 GMT</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTFBTYWhwS1hIUmZzRklFd0Rab1FCQ244MVMybHJYTEg2T1Y4STc3QWVxZlJEN0o4c2l3UTZvUFlqWVhYT3dQSktqaWRRSmFTQ3EwRVlld0xxeHhaQW5tYXIzZXpiaTJWcDlVY21JS283SEdHTDJKdkl3OVJDdUY?oc=5</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>google_rss</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>it</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>IT</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>IT:it</t>
-        </is>
-      </c>
-      <c r="K64" s="1" t="n">
-        <v>46135.36784722222</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>High Level City Italy Italian</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>("Milano" OR "Bologna") AND (protesta OR manifestazione OR corteo OR sciopero OR blocco OR presidio OR "sit-in") AND -calcio AND -moda AND -"settimana della moda" AND -Serie AND -mercato</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Milano, Sala “Cortei per il 25 aprile divisi? Occasione per portare avanti le proprie idee” - Pavia Uno TV</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>Milan, Room "Divided marches for April 25th? An opportunity to bring forward one's ideas" - Pavia Uno TV</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>Thu, 23 Apr 2026 12:43:27 GMT</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxQMUNwTEJGal9WaXRuSjFsbE95dE0tTm5fZFZ3ZEpycmVqaUxfY2taMjIzalpyM0JUTmdPMldib1E5b0w1aU55eFZWWmhNc0FQU2E4RnBsWHVidWRGU05pSmFVa1pIZzRVS25xOExrU1JGSUt0dkktbnE1b3M4TTFKNzQtTHVnX1pXcmgzbkZITl8tLWE4bjhXRGxqa0o1MjBsdi11ZkVvN3pHV0o5REczUnRvSjnSAbwBQVVfeXFMTk5rSUliR3FFREU1amVGRXRjbTJsRkFrRXJ3SGlsVlZ2WDhpTFVycEpaeW8tTFJKUXNUVUN4cm1KNUJnOTB1SDhMY2FYTklYOHRfZGhBNlFNNm1iTXdaMEN5UTdVYk83RjAwQ2lwdnExSHZzQWVBN3dMNW9JYkoyRm02dkhwZ0E4Q3o0dUxzcXpTSmg0Q2gxNnlfUkhhR1d5d3lmY21XXy1qNmhjeUZDYVcxRWdiZzBtOHJ2YVE?oc=5</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>google_rss</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>it</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>IT</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>IT:it</t>
-        </is>
-      </c>
-      <c r="K65" s="1" t="n">
-        <v>46135.53017361111</v>
+        <v>46136.31869212963</v>
       </c>
     </row>
   </sheetData>
